--- a/analysis/01_proximity_results.xlsx
+++ b/analysis/01_proximity_results.xlsx
@@ -611,10 +611,10 @@
       <c r="R2" t="n">
         <v>16</v>
       </c>
-      <c r="S2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T2" t="b">
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="inlineStr">
@@ -694,10 +694,10 @@
       <c r="R3" t="n">
         <v>-11</v>
       </c>
-      <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" t="b">
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr">
@@ -777,10 +777,10 @@
       <c r="R4" t="n">
         <v>3</v>
       </c>
-      <c r="S4" t="b">
-        <v>1</v>
-      </c>
-      <c r="T4" t="b">
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="inlineStr">
@@ -860,10 +860,10 @@
       <c r="R5" t="n">
         <v>8</v>
       </c>
-      <c r="S5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T5" t="b">
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="inlineStr">
@@ -943,10 +943,10 @@
       <c r="R6" t="n">
         <v>-1</v>
       </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr">
@@ -1026,10 +1026,10 @@
       <c r="R7" t="n">
         <v>7</v>
       </c>
-      <c r="S7" t="b">
-        <v>1</v>
-      </c>
-      <c r="T7" t="b">
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="inlineStr">
@@ -1109,10 +1109,10 @@
       <c r="R8" t="n">
         <v>-4</v>
       </c>
-      <c r="S8" t="b">
-        <v>0</v>
-      </c>
-      <c r="T8" t="b">
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr">
@@ -1192,10 +1192,10 @@
       <c r="R9" t="n">
         <v>17</v>
       </c>
-      <c r="S9" t="b">
-        <v>1</v>
-      </c>
-      <c r="T9" t="b">
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="inlineStr">
@@ -1275,10 +1275,10 @@
       <c r="R10" t="n">
         <v>25</v>
       </c>
-      <c r="S10" t="b">
-        <v>1</v>
-      </c>
-      <c r="T10" t="b">
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="inlineStr">
@@ -1358,10 +1358,10 @@
       <c r="R11" t="n">
         <v>12</v>
       </c>
-      <c r="S11" t="b">
-        <v>1</v>
-      </c>
-      <c r="T11" t="b">
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="inlineStr">
@@ -1441,10 +1441,10 @@
       <c r="R12" t="n">
         <v>-5</v>
       </c>
-      <c r="S12" t="b">
-        <v>0</v>
-      </c>
-      <c r="T12" t="b">
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr">
@@ -1524,10 +1524,10 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="b">
-        <v>0</v>
-      </c>
-      <c r="T13" t="b">
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="inlineStr">
@@ -1607,10 +1607,10 @@
       <c r="R14" t="n">
         <v>-2</v>
       </c>
-      <c r="S14" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" t="b">
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr">
@@ -1690,10 +1690,10 @@
       <c r="R15" t="n">
         <v>11</v>
       </c>
-      <c r="S15" t="b">
-        <v>1</v>
-      </c>
-      <c r="T15" t="b">
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="inlineStr">
@@ -1773,10 +1773,10 @@
       <c r="R16" t="n">
         <v>-6</v>
       </c>
-      <c r="S16" t="b">
-        <v>0</v>
-      </c>
-      <c r="T16" t="b">
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="inlineStr">
@@ -1856,10 +1856,10 @@
       <c r="R17" t="n">
         <v>22</v>
       </c>
-      <c r="S17" t="b">
-        <v>1</v>
-      </c>
-      <c r="T17" t="b">
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="inlineStr">
@@ -1939,10 +1939,10 @@
       <c r="R18" t="n">
         <v>-12</v>
       </c>
-      <c r="S18" t="b">
-        <v>0</v>
-      </c>
-      <c r="T18" t="b">
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="inlineStr">
@@ -2022,10 +2022,10 @@
       <c r="R19" t="n">
         <v>8</v>
       </c>
-      <c r="S19" t="b">
-        <v>1</v>
-      </c>
-      <c r="T19" t="b">
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="inlineStr">
@@ -2105,10 +2105,10 @@
       <c r="R20" t="n">
         <v>3</v>
       </c>
-      <c r="S20" t="b">
-        <v>1</v>
-      </c>
-      <c r="T20" t="b">
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="inlineStr">
@@ -2188,10 +2188,10 @@
       <c r="R21" t="n">
         <v>10</v>
       </c>
-      <c r="S21" t="b">
-        <v>1</v>
-      </c>
-      <c r="T21" t="b">
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="inlineStr">
@@ -2344,10 +2344,10 @@
       <c r="R23" t="n">
         <v>37</v>
       </c>
-      <c r="S23" t="b">
-        <v>1</v>
-      </c>
-      <c r="T23" t="b">
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="inlineStr">
@@ -2427,10 +2427,10 @@
       <c r="R24" t="n">
         <v>24</v>
       </c>
-      <c r="S24" t="b">
-        <v>1</v>
-      </c>
-      <c r="T24" t="b">
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="inlineStr">
@@ -2510,10 +2510,10 @@
       <c r="R25" t="n">
         <v>12</v>
       </c>
-      <c r="S25" t="b">
-        <v>1</v>
-      </c>
-      <c r="T25" t="b">
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="inlineStr">
@@ -2593,10 +2593,10 @@
       <c r="R26" t="n">
         <v>11</v>
       </c>
-      <c r="S26" t="b">
-        <v>1</v>
-      </c>
-      <c r="T26" t="b">
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="inlineStr">
@@ -2676,10 +2676,10 @@
       <c r="R27" t="n">
         <v>22</v>
       </c>
-      <c r="S27" t="b">
-        <v>1</v>
-      </c>
-      <c r="T27" t="b">
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="inlineStr">
@@ -2759,10 +2759,10 @@
       <c r="R28" t="n">
         <v>8</v>
       </c>
-      <c r="S28" t="b">
-        <v>1</v>
-      </c>
-      <c r="T28" t="b">
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
         <v>0</v>
       </c>
       <c r="U28" t="inlineStr">
@@ -2840,10 +2840,10 @@
       <c r="R29" t="n">
         <v>-3</v>
       </c>
-      <c r="S29" t="b">
-        <v>0</v>
-      </c>
-      <c r="T29" t="b">
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="inlineStr">
@@ -2923,10 +2923,10 @@
       <c r="R30" t="n">
         <v>-5</v>
       </c>
-      <c r="S30" t="b">
-        <v>0</v>
-      </c>
-      <c r="T30" t="b">
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="U30" t="inlineStr">
@@ -3006,10 +3006,10 @@
       <c r="R31" t="n">
         <v>7</v>
       </c>
-      <c r="S31" t="b">
-        <v>1</v>
-      </c>
-      <c r="T31" t="b">
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
         <v>0</v>
       </c>
       <c r="U31" t="inlineStr">
@@ -3089,10 +3089,10 @@
       <c r="R32" t="n">
         <v>-15</v>
       </c>
-      <c r="S32" t="b">
-        <v>0</v>
-      </c>
-      <c r="T32" t="b">
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="inlineStr">
@@ -3172,10 +3172,10 @@
       <c r="R33" t="n">
         <v>22</v>
       </c>
-      <c r="S33" t="b">
-        <v>1</v>
-      </c>
-      <c r="T33" t="b">
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="inlineStr">
@@ -3255,10 +3255,10 @@
       <c r="R34" t="n">
         <v>25</v>
       </c>
-      <c r="S34" t="b">
-        <v>1</v>
-      </c>
-      <c r="T34" t="b">
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
         <v>0</v>
       </c>
       <c r="U34" t="inlineStr">
@@ -3338,10 +3338,10 @@
       <c r="R35" t="n">
         <v>18</v>
       </c>
-      <c r="S35" t="b">
-        <v>1</v>
-      </c>
-      <c r="T35" t="b">
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
         <v>0</v>
       </c>
       <c r="U35" t="inlineStr">
@@ -3421,10 +3421,10 @@
       <c r="R36" t="n">
         <v>-3</v>
       </c>
-      <c r="S36" t="b">
-        <v>0</v>
-      </c>
-      <c r="T36" t="b">
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="inlineStr">
@@ -3504,10 +3504,10 @@
       <c r="R37" t="n">
         <v>30</v>
       </c>
-      <c r="S37" t="b">
-        <v>1</v>
-      </c>
-      <c r="T37" t="b">
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="inlineStr">
@@ -3587,10 +3587,10 @@
       <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="S38" t="b">
-        <v>1</v>
-      </c>
-      <c r="T38" t="b">
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
         <v>0</v>
       </c>
       <c r="U38" t="inlineStr">
@@ -3670,10 +3670,10 @@
       <c r="R39" t="n">
         <v>-4</v>
       </c>
-      <c r="S39" t="b">
-        <v>0</v>
-      </c>
-      <c r="T39" t="b">
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="inlineStr">
@@ -3753,10 +3753,10 @@
       <c r="R40" t="n">
         <v>-1</v>
       </c>
-      <c r="S40" t="b">
-        <v>0</v>
-      </c>
-      <c r="T40" t="b">
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="inlineStr">
@@ -3836,10 +3836,10 @@
       <c r="R41" t="n">
         <v>34</v>
       </c>
-      <c r="S41" t="b">
-        <v>1</v>
-      </c>
-      <c r="T41" t="b">
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
         <v>0</v>
       </c>
       <c r="U41" t="inlineStr">
@@ -3919,10 +3919,10 @@
       <c r="R42" t="n">
         <v>24</v>
       </c>
-      <c r="S42" t="b">
-        <v>1</v>
-      </c>
-      <c r="T42" t="b">
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="inlineStr">
@@ -4002,10 +4002,10 @@
       <c r="R43" t="n">
         <v>20</v>
       </c>
-      <c r="S43" t="b">
-        <v>1</v>
-      </c>
-      <c r="T43" t="b">
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
         <v>0</v>
       </c>
       <c r="U43" t="inlineStr">
@@ -4085,10 +4085,10 @@
       <c r="R44" t="n">
         <v>4</v>
       </c>
-      <c r="S44" t="b">
-        <v>1</v>
-      </c>
-      <c r="T44" t="b">
+      <c r="S44" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
         <v>0</v>
       </c>
       <c r="U44" t="inlineStr">
@@ -4168,10 +4168,10 @@
       <c r="R45" t="n">
         <v>2</v>
       </c>
-      <c r="S45" t="b">
-        <v>1</v>
-      </c>
-      <c r="T45" t="b">
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="inlineStr">
@@ -4251,10 +4251,10 @@
       <c r="R46" t="n">
         <v>17</v>
       </c>
-      <c r="S46" t="b">
-        <v>1</v>
-      </c>
-      <c r="T46" t="b">
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
         <v>0</v>
       </c>
       <c r="U46" t="inlineStr">
@@ -4334,10 +4334,10 @@
       <c r="R47" t="n">
         <v>-4</v>
       </c>
-      <c r="S47" t="b">
-        <v>0</v>
-      </c>
-      <c r="T47" t="b">
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="inlineStr">
@@ -4417,10 +4417,10 @@
       <c r="R48" t="n">
         <v>10</v>
       </c>
-      <c r="S48" t="b">
-        <v>1</v>
-      </c>
-      <c r="T48" t="b">
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
         <v>0</v>
       </c>
       <c r="U48" t="inlineStr">
@@ -4500,10 +4500,10 @@
       <c r="R49" t="n">
         <v>-3</v>
       </c>
-      <c r="S49" t="b">
-        <v>0</v>
-      </c>
-      <c r="T49" t="b">
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="inlineStr">
@@ -4583,10 +4583,10 @@
       <c r="R50" t="n">
         <v>21</v>
       </c>
-      <c r="S50" t="b">
-        <v>1</v>
-      </c>
-      <c r="T50" t="b">
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
         <v>0</v>
       </c>
       <c r="U50" t="inlineStr">
@@ -4666,10 +4666,10 @@
       <c r="R51" t="n">
         <v>16</v>
       </c>
-      <c r="S51" t="b">
-        <v>1</v>
-      </c>
-      <c r="T51" t="b">
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
         <v>0</v>
       </c>
       <c r="U51" t="inlineStr">
@@ -4749,10 +4749,10 @@
       <c r="R52" t="n">
         <v>25</v>
       </c>
-      <c r="S52" t="b">
-        <v>1</v>
-      </c>
-      <c r="T52" t="b">
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
         <v>0</v>
       </c>
       <c r="U52" t="inlineStr">
@@ -4832,10 +4832,10 @@
       <c r="R53" t="n">
         <v>28</v>
       </c>
-      <c r="S53" t="b">
-        <v>1</v>
-      </c>
-      <c r="T53" t="b">
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
         <v>0</v>
       </c>
       <c r="U53" t="inlineStr">
@@ -4915,10 +4915,10 @@
       <c r="R54" t="n">
         <v>-2</v>
       </c>
-      <c r="S54" t="b">
-        <v>0</v>
-      </c>
-      <c r="T54" t="b">
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
         <v>1</v>
       </c>
       <c r="U54" t="inlineStr">
@@ -4998,10 +4998,10 @@
       <c r="R55" t="n">
         <v>-3</v>
       </c>
-      <c r="S55" t="b">
-        <v>0</v>
-      </c>
-      <c r="T55" t="b">
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="inlineStr">
@@ -5081,10 +5081,10 @@
       <c r="R56" t="n">
         <v>25</v>
       </c>
-      <c r="S56" t="b">
-        <v>1</v>
-      </c>
-      <c r="T56" t="b">
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
         <v>0</v>
       </c>
       <c r="U56" t="inlineStr">
@@ -5164,10 +5164,10 @@
       <c r="R57" t="n">
         <v>6</v>
       </c>
-      <c r="S57" t="b">
-        <v>1</v>
-      </c>
-      <c r="T57" t="b">
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
         <v>0</v>
       </c>
       <c r="U57" t="inlineStr">
@@ -5247,10 +5247,10 @@
       <c r="R58" t="n">
         <v>2</v>
       </c>
-      <c r="S58" t="b">
-        <v>1</v>
-      </c>
-      <c r="T58" t="b">
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
         <v>0</v>
       </c>
       <c r="U58" t="inlineStr">
@@ -5330,10 +5330,10 @@
       <c r="R59" t="n">
         <v>36</v>
       </c>
-      <c r="S59" t="b">
-        <v>1</v>
-      </c>
-      <c r="T59" t="b">
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
         <v>0</v>
       </c>
       <c r="U59" t="inlineStr">
@@ -5413,10 +5413,10 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="b">
-        <v>0</v>
-      </c>
-      <c r="T60" t="b">
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
         <v>0</v>
       </c>
       <c r="U60" t="inlineStr">
@@ -5496,10 +5496,10 @@
       <c r="R61" t="n">
         <v>23</v>
       </c>
-      <c r="S61" t="b">
-        <v>1</v>
-      </c>
-      <c r="T61" t="b">
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
         <v>0</v>
       </c>
       <c r="U61" t="inlineStr">
@@ -5579,10 +5579,10 @@
       <c r="R62" t="n">
         <v>23</v>
       </c>
-      <c r="S62" t="b">
-        <v>1</v>
-      </c>
-      <c r="T62" t="b">
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
         <v>0</v>
       </c>
       <c r="U62" t="inlineStr">
@@ -5662,10 +5662,10 @@
       <c r="R63" t="n">
         <v>-3</v>
       </c>
-      <c r="S63" t="b">
-        <v>0</v>
-      </c>
-      <c r="T63" t="b">
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="inlineStr">
@@ -5818,10 +5818,10 @@
       <c r="R65" t="n">
         <v>24</v>
       </c>
-      <c r="S65" t="b">
-        <v>1</v>
-      </c>
-      <c r="T65" t="b">
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
         <v>0</v>
       </c>
       <c r="U65" t="inlineStr">
@@ -5901,10 +5901,10 @@
       <c r="R66" t="n">
         <v>21</v>
       </c>
-      <c r="S66" t="b">
-        <v>1</v>
-      </c>
-      <c r="T66" t="b">
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
         <v>0</v>
       </c>
       <c r="U66" t="inlineStr">
@@ -5984,10 +5984,10 @@
       <c r="R67" t="n">
         <v>25</v>
       </c>
-      <c r="S67" t="b">
-        <v>1</v>
-      </c>
-      <c r="T67" t="b">
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
         <v>0</v>
       </c>
       <c r="U67" t="inlineStr">
@@ -6067,10 +6067,10 @@
       <c r="R68" t="n">
         <v>28</v>
       </c>
-      <c r="S68" t="b">
-        <v>1</v>
-      </c>
-      <c r="T68" t="b">
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
         <v>0</v>
       </c>
       <c r="U68" t="inlineStr">
@@ -6150,10 +6150,10 @@
       <c r="R69" t="n">
         <v>-14</v>
       </c>
-      <c r="S69" t="b">
-        <v>0</v>
-      </c>
-      <c r="T69" t="b">
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
         <v>1</v>
       </c>
       <c r="U69" t="inlineStr">
@@ -6233,10 +6233,10 @@
       <c r="R70" t="n">
         <v>1</v>
       </c>
-      <c r="S70" t="b">
-        <v>1</v>
-      </c>
-      <c r="T70" t="b">
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
         <v>0</v>
       </c>
       <c r="U70" t="inlineStr">
@@ -6316,10 +6316,10 @@
       <c r="R71" t="n">
         <v>12</v>
       </c>
-      <c r="S71" t="b">
-        <v>1</v>
-      </c>
-      <c r="T71" t="b">
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
         <v>0</v>
       </c>
       <c r="U71" t="inlineStr">
@@ -6399,10 +6399,10 @@
       <c r="R72" t="n">
         <v>15</v>
       </c>
-      <c r="S72" t="b">
-        <v>1</v>
-      </c>
-      <c r="T72" t="b">
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
         <v>0</v>
       </c>
       <c r="U72" t="inlineStr">
@@ -6555,10 +6555,10 @@
       <c r="R74" t="n">
         <v>20</v>
       </c>
-      <c r="S74" t="b">
-        <v>1</v>
-      </c>
-      <c r="T74" t="b">
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
         <v>0</v>
       </c>
       <c r="U74" t="inlineStr">
@@ -6638,10 +6638,10 @@
       <c r="R75" t="n">
         <v>-7</v>
       </c>
-      <c r="S75" t="b">
-        <v>0</v>
-      </c>
-      <c r="T75" t="b">
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="inlineStr">
@@ -6721,10 +6721,10 @@
       <c r="R76" t="n">
         <v>12</v>
       </c>
-      <c r="S76" t="b">
-        <v>1</v>
-      </c>
-      <c r="T76" t="b">
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
         <v>0</v>
       </c>
       <c r="U76" t="inlineStr">
@@ -6804,10 +6804,10 @@
       <c r="R77" t="n">
         <v>4</v>
       </c>
-      <c r="S77" t="b">
-        <v>1</v>
-      </c>
-      <c r="T77" t="b">
+      <c r="S77" t="n">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
         <v>0</v>
       </c>
       <c r="U77" t="inlineStr">
@@ -6887,10 +6887,10 @@
       <c r="R78" t="n">
         <v>37</v>
       </c>
-      <c r="S78" t="b">
-        <v>1</v>
-      </c>
-      <c r="T78" t="b">
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
         <v>0</v>
       </c>
       <c r="U78" t="inlineStr">
@@ -6970,10 +6970,10 @@
       <c r="R79" t="n">
         <v>15</v>
       </c>
-      <c r="S79" t="b">
-        <v>1</v>
-      </c>
-      <c r="T79" t="b">
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
         <v>0</v>
       </c>
       <c r="U79" t="inlineStr">
@@ -7053,10 +7053,10 @@
       <c r="R80" t="n">
         <v>4</v>
       </c>
-      <c r="S80" t="b">
-        <v>1</v>
-      </c>
-      <c r="T80" t="b">
+      <c r="S80" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
         <v>0</v>
       </c>
       <c r="U80" t="inlineStr">
@@ -7209,10 +7209,10 @@
       <c r="R82" t="n">
         <v>12</v>
       </c>
-      <c r="S82" t="b">
-        <v>1</v>
-      </c>
-      <c r="T82" t="b">
+      <c r="S82" t="n">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
         <v>0</v>
       </c>
       <c r="U82" t="inlineStr">
@@ -7292,10 +7292,10 @@
       <c r="R83" t="n">
         <v>-1</v>
       </c>
-      <c r="S83" t="b">
-        <v>0</v>
-      </c>
-      <c r="T83" t="b">
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
         <v>1</v>
       </c>
       <c r="U83" t="inlineStr">
@@ -7448,10 +7448,10 @@
       <c r="R85" t="n">
         <v>-5</v>
       </c>
-      <c r="S85" t="b">
-        <v>0</v>
-      </c>
-      <c r="T85" t="b">
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
         <v>1</v>
       </c>
       <c r="U85" t="inlineStr">
@@ -7531,10 +7531,10 @@
       <c r="R86" t="n">
         <v>9</v>
       </c>
-      <c r="S86" t="b">
-        <v>1</v>
-      </c>
-      <c r="T86" t="b">
+      <c r="S86" t="n">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
         <v>0</v>
       </c>
       <c r="U86" t="inlineStr">
@@ -7614,10 +7614,10 @@
       <c r="R87" t="n">
         <v>-11</v>
       </c>
-      <c r="S87" t="b">
-        <v>0</v>
-      </c>
-      <c r="T87" t="b">
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
         <v>1</v>
       </c>
       <c r="U87" t="inlineStr">
@@ -7650,7 +7650,9 @@
           <t>Farm-Service Town, Icelandic Settlement, Organized/Ethnic Settlement, Small Service Centre</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>1882</v>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>18461.4</v>
@@ -7916,10 +7918,10 @@
       <c r="R91" t="n">
         <v>-4</v>
       </c>
-      <c r="S91" t="b">
-        <v>0</v>
-      </c>
-      <c r="T91" t="b">
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
         <v>1</v>
       </c>
       <c r="U91" t="inlineStr">
@@ -7999,10 +8001,10 @@
       <c r="R92" t="n">
         <v>-2</v>
       </c>
-      <c r="S92" t="b">
-        <v>0</v>
-      </c>
-      <c r="T92" t="b">
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
         <v>1</v>
       </c>
       <c r="U92" t="inlineStr">
@@ -8082,10 +8084,10 @@
       <c r="R93" t="n">
         <v>3</v>
       </c>
-      <c r="S93" t="b">
-        <v>1</v>
-      </c>
-      <c r="T93" t="b">
+      <c r="S93" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
         <v>0</v>
       </c>
       <c r="U93" t="inlineStr">
@@ -8165,10 +8167,10 @@
       <c r="R94" t="n">
         <v>15</v>
       </c>
-      <c r="S94" t="b">
-        <v>1</v>
-      </c>
-      <c r="T94" t="b">
+      <c r="S94" t="n">
+        <v>1</v>
+      </c>
+      <c r="T94" t="n">
         <v>0</v>
       </c>
       <c r="U94" t="inlineStr">
@@ -8248,10 +8250,10 @@
       <c r="R95" t="n">
         <v>18</v>
       </c>
-      <c r="S95" t="b">
-        <v>1</v>
-      </c>
-      <c r="T95" t="b">
+      <c r="S95" t="n">
+        <v>1</v>
+      </c>
+      <c r="T95" t="n">
         <v>0</v>
       </c>
       <c r="U95" t="inlineStr">
@@ -8331,10 +8333,10 @@
       <c r="R96" t="n">
         <v>24</v>
       </c>
-      <c r="S96" t="b">
-        <v>1</v>
-      </c>
-      <c r="T96" t="b">
+      <c r="S96" t="n">
+        <v>1</v>
+      </c>
+      <c r="T96" t="n">
         <v>0</v>
       </c>
       <c r="U96" t="inlineStr">
@@ -8414,10 +8416,10 @@
       <c r="R97" t="n">
         <v>1</v>
       </c>
-      <c r="S97" t="b">
-        <v>1</v>
-      </c>
-      <c r="T97" t="b">
+      <c r="S97" t="n">
+        <v>1</v>
+      </c>
+      <c r="T97" t="n">
         <v>0</v>
       </c>
       <c r="U97" t="inlineStr">
@@ -8497,10 +8499,10 @@
       <c r="R98" t="n">
         <v>29</v>
       </c>
-      <c r="S98" t="b">
-        <v>1</v>
-      </c>
-      <c r="T98" t="b">
+      <c r="S98" t="n">
+        <v>1</v>
+      </c>
+      <c r="T98" t="n">
         <v>0</v>
       </c>
       <c r="U98" t="inlineStr">
@@ -8580,10 +8582,10 @@
       <c r="R99" t="n">
         <v>13</v>
       </c>
-      <c r="S99" t="b">
-        <v>1</v>
-      </c>
-      <c r="T99" t="b">
+      <c r="S99" t="n">
+        <v>1</v>
+      </c>
+      <c r="T99" t="n">
         <v>0</v>
       </c>
       <c r="U99" t="inlineStr">
@@ -8663,10 +8665,10 @@
       <c r="R100" t="n">
         <v>20</v>
       </c>
-      <c r="S100" t="b">
-        <v>1</v>
-      </c>
-      <c r="T100" t="b">
+      <c r="S100" t="n">
+        <v>1</v>
+      </c>
+      <c r="T100" t="n">
         <v>0</v>
       </c>
       <c r="U100" t="inlineStr">
@@ -8746,10 +8748,10 @@
       <c r="R101" t="n">
         <v>-3</v>
       </c>
-      <c r="S101" t="b">
-        <v>0</v>
-      </c>
-      <c r="T101" t="b">
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
         <v>1</v>
       </c>
       <c r="U101" t="inlineStr">
@@ -8829,10 +8831,10 @@
       <c r="R102" t="n">
         <v>12</v>
       </c>
-      <c r="S102" t="b">
-        <v>1</v>
-      </c>
-      <c r="T102" t="b">
+      <c r="S102" t="n">
+        <v>1</v>
+      </c>
+      <c r="T102" t="n">
         <v>0</v>
       </c>
       <c r="U102" t="inlineStr">
@@ -8912,10 +8914,10 @@
       <c r="R103" t="n">
         <v>1</v>
       </c>
-      <c r="S103" t="b">
-        <v>1</v>
-      </c>
-      <c r="T103" t="b">
+      <c r="S103" t="n">
+        <v>1</v>
+      </c>
+      <c r="T103" t="n">
         <v>0</v>
       </c>
       <c r="U103" t="inlineStr">
@@ -8995,10 +8997,10 @@
       <c r="R104" t="n">
         <v>7</v>
       </c>
-      <c r="S104" t="b">
-        <v>1</v>
-      </c>
-      <c r="T104" t="b">
+      <c r="S104" t="n">
+        <v>1</v>
+      </c>
+      <c r="T104" t="n">
         <v>0</v>
       </c>
       <c r="U104" t="inlineStr">
@@ -9078,10 +9080,10 @@
       <c r="R105" t="n">
         <v>-2</v>
       </c>
-      <c r="S105" t="b">
-        <v>0</v>
-      </c>
-      <c r="T105" t="b">
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
         <v>1</v>
       </c>
       <c r="U105" t="inlineStr">
@@ -9115,7 +9117,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="G106" t="n">
         <v>1907</v>
@@ -9161,10 +9163,10 @@
       <c r="R106" t="n">
         <v>22</v>
       </c>
-      <c r="S106" t="b">
-        <v>1</v>
-      </c>
-      <c r="T106" t="b">
+      <c r="S106" t="n">
+        <v>1</v>
+      </c>
+      <c r="T106" t="n">
         <v>0</v>
       </c>
       <c r="U106" t="inlineStr">
@@ -9244,10 +9246,10 @@
       <c r="R107" t="n">
         <v>5</v>
       </c>
-      <c r="S107" t="b">
-        <v>1</v>
-      </c>
-      <c r="T107" t="b">
+      <c r="S107" t="n">
+        <v>1</v>
+      </c>
+      <c r="T107" t="n">
         <v>0</v>
       </c>
       <c r="U107" t="inlineStr">
@@ -9327,10 +9329,10 @@
       <c r="R108" t="n">
         <v>37</v>
       </c>
-      <c r="S108" t="b">
-        <v>1</v>
-      </c>
-      <c r="T108" t="b">
+      <c r="S108" t="n">
+        <v>1</v>
+      </c>
+      <c r="T108" t="n">
         <v>0</v>
       </c>
       <c r="U108" t="inlineStr">
@@ -9410,10 +9412,10 @@
       <c r="R109" t="n">
         <v>13</v>
       </c>
-      <c r="S109" t="b">
-        <v>1</v>
-      </c>
-      <c r="T109" t="b">
+      <c r="S109" t="n">
+        <v>1</v>
+      </c>
+      <c r="T109" t="n">
         <v>0</v>
       </c>
       <c r="U109" t="inlineStr">
@@ -9493,10 +9495,10 @@
       <c r="R110" t="n">
         <v>24</v>
       </c>
-      <c r="S110" t="b">
-        <v>1</v>
-      </c>
-      <c r="T110" t="b">
+      <c r="S110" t="n">
+        <v>1</v>
+      </c>
+      <c r="T110" t="n">
         <v>0</v>
       </c>
       <c r="U110" t="inlineStr">
@@ -9576,10 +9578,10 @@
       <c r="R111" t="n">
         <v>20</v>
       </c>
-      <c r="S111" t="b">
-        <v>1</v>
-      </c>
-      <c r="T111" t="b">
+      <c r="S111" t="n">
+        <v>1</v>
+      </c>
+      <c r="T111" t="n">
         <v>0</v>
       </c>
       <c r="U111" t="inlineStr">
@@ -9659,10 +9661,10 @@
       <c r="R112" t="n">
         <v>4</v>
       </c>
-      <c r="S112" t="b">
-        <v>1</v>
-      </c>
-      <c r="T112" t="b">
+      <c r="S112" t="n">
+        <v>1</v>
+      </c>
+      <c r="T112" t="n">
         <v>0</v>
       </c>
       <c r="U112" t="inlineStr">
@@ -9742,10 +9744,10 @@
       <c r="R113" t="n">
         <v>14</v>
       </c>
-      <c r="S113" t="b">
-        <v>1</v>
-      </c>
-      <c r="T113" t="b">
+      <c r="S113" t="n">
+        <v>1</v>
+      </c>
+      <c r="T113" t="n">
         <v>0</v>
       </c>
       <c r="U113" t="inlineStr">
@@ -9825,10 +9827,10 @@
       <c r="R114" t="n">
         <v>-1</v>
       </c>
-      <c r="S114" t="b">
-        <v>0</v>
-      </c>
-      <c r="T114" t="b">
+      <c r="S114" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" t="n">
         <v>1</v>
       </c>
       <c r="U114" t="inlineStr">
@@ -9908,10 +9910,10 @@
       <c r="R115" t="n">
         <v>0</v>
       </c>
-      <c r="S115" t="b">
-        <v>0</v>
-      </c>
-      <c r="T115" t="b">
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
         <v>0</v>
       </c>
       <c r="U115" t="inlineStr">
@@ -9991,10 +9993,10 @@
       <c r="R116" t="n">
         <v>-1</v>
       </c>
-      <c r="S116" t="b">
-        <v>0</v>
-      </c>
-      <c r="T116" t="b">
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
         <v>1</v>
       </c>
       <c r="U116" t="inlineStr">
@@ -10074,10 +10076,10 @@
       <c r="R117" t="n">
         <v>25</v>
       </c>
-      <c r="S117" t="b">
-        <v>1</v>
-      </c>
-      <c r="T117" t="b">
+      <c r="S117" t="n">
+        <v>1</v>
+      </c>
+      <c r="T117" t="n">
         <v>0</v>
       </c>
       <c r="U117" t="inlineStr">
@@ -10157,10 +10159,10 @@
       <c r="R118" t="n">
         <v>-3</v>
       </c>
-      <c r="S118" t="b">
-        <v>0</v>
-      </c>
-      <c r="T118" t="b">
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
         <v>1</v>
       </c>
       <c r="U118" t="inlineStr">
@@ -10240,10 +10242,10 @@
       <c r="R119" t="n">
         <v>-4</v>
       </c>
-      <c r="S119" t="b">
-        <v>0</v>
-      </c>
-      <c r="T119" t="b">
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
         <v>1</v>
       </c>
       <c r="U119" t="inlineStr">
@@ -10323,10 +10325,10 @@
       <c r="R120" t="n">
         <v>7</v>
       </c>
-      <c r="S120" t="b">
-        <v>1</v>
-      </c>
-      <c r="T120" t="b">
+      <c r="S120" t="n">
+        <v>1</v>
+      </c>
+      <c r="T120" t="n">
         <v>0</v>
       </c>
       <c r="U120" t="inlineStr">
@@ -10479,10 +10481,10 @@
       <c r="R122" t="n">
         <v>25</v>
       </c>
-      <c r="S122" t="b">
-        <v>1</v>
-      </c>
-      <c r="T122" t="b">
+      <c r="S122" t="n">
+        <v>1</v>
+      </c>
+      <c r="T122" t="n">
         <v>0</v>
       </c>
       <c r="U122" t="inlineStr">
@@ -10562,10 +10564,10 @@
       <c r="R123" t="n">
         <v>-6</v>
       </c>
-      <c r="S123" t="b">
-        <v>0</v>
-      </c>
-      <c r="T123" t="b">
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
         <v>1</v>
       </c>
       <c r="U123" t="inlineStr">
@@ -10645,10 +10647,10 @@
       <c r="R124" t="n">
         <v>-3</v>
       </c>
-      <c r="S124" t="b">
-        <v>0</v>
-      </c>
-      <c r="T124" t="b">
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
         <v>1</v>
       </c>
       <c r="U124" t="inlineStr">
@@ -10728,10 +10730,10 @@
       <c r="R125" t="n">
         <v>14</v>
       </c>
-      <c r="S125" t="b">
-        <v>1</v>
-      </c>
-      <c r="T125" t="b">
+      <c r="S125" t="n">
+        <v>1</v>
+      </c>
+      <c r="T125" t="n">
         <v>0</v>
       </c>
       <c r="U125" t="inlineStr">
@@ -10811,10 +10813,10 @@
       <c r="R126" t="n">
         <v>9</v>
       </c>
-      <c r="S126" t="b">
-        <v>1</v>
-      </c>
-      <c r="T126" t="b">
+      <c r="S126" t="n">
+        <v>1</v>
+      </c>
+      <c r="T126" t="n">
         <v>0</v>
       </c>
       <c r="U126" t="inlineStr">
@@ -10894,10 +10896,10 @@
       <c r="R127" t="n">
         <v>-8</v>
       </c>
-      <c r="S127" t="b">
-        <v>0</v>
-      </c>
-      <c r="T127" t="b">
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
         <v>1</v>
       </c>
       <c r="U127" t="inlineStr">
@@ -10975,10 +10977,10 @@
       <c r="R128" t="n">
         <v>37</v>
       </c>
-      <c r="S128" t="b">
-        <v>1</v>
-      </c>
-      <c r="T128" t="b">
+      <c r="S128" t="n">
+        <v>1</v>
+      </c>
+      <c r="T128" t="n">
         <v>0</v>
       </c>
       <c r="U128" t="inlineStr">
@@ -11058,10 +11060,10 @@
       <c r="R129" t="n">
         <v>5</v>
       </c>
-      <c r="S129" t="b">
-        <v>1</v>
-      </c>
-      <c r="T129" t="b">
+      <c r="S129" t="n">
+        <v>1</v>
+      </c>
+      <c r="T129" t="n">
         <v>0</v>
       </c>
       <c r="U129" t="inlineStr">
@@ -11141,10 +11143,10 @@
       <c r="R130" t="n">
         <v>-5</v>
       </c>
-      <c r="S130" t="b">
-        <v>0</v>
-      </c>
-      <c r="T130" t="b">
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
         <v>1</v>
       </c>
       <c r="U130" t="inlineStr">
@@ -11224,10 +11226,10 @@
       <c r="R131" t="n">
         <v>9</v>
       </c>
-      <c r="S131" t="b">
-        <v>1</v>
-      </c>
-      <c r="T131" t="b">
+      <c r="S131" t="n">
+        <v>1</v>
+      </c>
+      <c r="T131" t="n">
         <v>0</v>
       </c>
       <c r="U131" t="inlineStr">
@@ -11453,10 +11455,10 @@
       <c r="R134" t="n">
         <v>12</v>
       </c>
-      <c r="S134" t="b">
-        <v>1</v>
-      </c>
-      <c r="T134" t="b">
+      <c r="S134" t="n">
+        <v>1</v>
+      </c>
+      <c r="T134" t="n">
         <v>0</v>
       </c>
       <c r="U134" t="inlineStr">
@@ -11534,10 +11536,10 @@
       <c r="R135" t="n">
         <v>-2</v>
       </c>
-      <c r="S135" t="b">
-        <v>0</v>
-      </c>
-      <c r="T135" t="b">
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
         <v>1</v>
       </c>
       <c r="U135" t="inlineStr">
@@ -11617,10 +11619,10 @@
       <c r="R136" t="n">
         <v>34</v>
       </c>
-      <c r="S136" t="b">
-        <v>1</v>
-      </c>
-      <c r="T136" t="b">
+      <c r="S136" t="n">
+        <v>1</v>
+      </c>
+      <c r="T136" t="n">
         <v>0</v>
       </c>
       <c r="U136" t="inlineStr">
@@ -11700,10 +11702,10 @@
       <c r="R137" t="n">
         <v>-5</v>
       </c>
-      <c r="S137" t="b">
-        <v>0</v>
-      </c>
-      <c r="T137" t="b">
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
         <v>1</v>
       </c>
       <c r="U137" t="inlineStr">
@@ -11783,10 +11785,10 @@
       <c r="R138" t="n">
         <v>1</v>
       </c>
-      <c r="S138" t="b">
-        <v>1</v>
-      </c>
-      <c r="T138" t="b">
+      <c r="S138" t="n">
+        <v>1</v>
+      </c>
+      <c r="T138" t="n">
         <v>0</v>
       </c>
       <c r="U138" t="inlineStr">
@@ -11866,10 +11868,10 @@
       <c r="R139" t="n">
         <v>-2</v>
       </c>
-      <c r="S139" t="b">
-        <v>0</v>
-      </c>
-      <c r="T139" t="b">
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
         <v>1</v>
       </c>
       <c r="U139" t="inlineStr">
@@ -11949,10 +11951,10 @@
       <c r="R140" t="n">
         <v>3</v>
       </c>
-      <c r="S140" t="b">
-        <v>1</v>
-      </c>
-      <c r="T140" t="b">
+      <c r="S140" t="n">
+        <v>1</v>
+      </c>
+      <c r="T140" t="n">
         <v>0</v>
       </c>
       <c r="U140" t="inlineStr">
@@ -12032,10 +12034,10 @@
       <c r="R141" t="n">
         <v>1</v>
       </c>
-      <c r="S141" t="b">
-        <v>1</v>
-      </c>
-      <c r="T141" t="b">
+      <c r="S141" t="n">
+        <v>1</v>
+      </c>
+      <c r="T141" t="n">
         <v>0</v>
       </c>
       <c r="U141" t="inlineStr">
@@ -12115,10 +12117,10 @@
       <c r="R142" t="n">
         <v>8</v>
       </c>
-      <c r="S142" t="b">
-        <v>1</v>
-      </c>
-      <c r="T142" t="b">
+      <c r="S142" t="n">
+        <v>1</v>
+      </c>
+      <c r="T142" t="n">
         <v>0</v>
       </c>
       <c r="U142" t="inlineStr">
@@ -12198,10 +12200,10 @@
       <c r="R143" t="n">
         <v>2</v>
       </c>
-      <c r="S143" t="b">
-        <v>1</v>
-      </c>
-      <c r="T143" t="b">
+      <c r="S143" t="n">
+        <v>1</v>
+      </c>
+      <c r="T143" t="n">
         <v>0</v>
       </c>
       <c r="U143" t="inlineStr">
@@ -12281,10 +12283,10 @@
       <c r="R144" t="n">
         <v>-1</v>
       </c>
-      <c r="S144" t="b">
-        <v>0</v>
-      </c>
-      <c r="T144" t="b">
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
         <v>1</v>
       </c>
       <c r="U144" t="inlineStr">
@@ -12364,10 +12366,10 @@
       <c r="R145" t="n">
         <v>2</v>
       </c>
-      <c r="S145" t="b">
-        <v>1</v>
-      </c>
-      <c r="T145" t="b">
+      <c r="S145" t="n">
+        <v>1</v>
+      </c>
+      <c r="T145" t="n">
         <v>0</v>
       </c>
       <c r="U145" t="inlineStr">
@@ -12447,10 +12449,10 @@
       <c r="R146" t="n">
         <v>-1</v>
       </c>
-      <c r="S146" t="b">
-        <v>0</v>
-      </c>
-      <c r="T146" t="b">
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
         <v>1</v>
       </c>
       <c r="U146" t="inlineStr">
@@ -12530,10 +12532,10 @@
       <c r="R147" t="n">
         <v>4</v>
       </c>
-      <c r="S147" t="b">
-        <v>1</v>
-      </c>
-      <c r="T147" t="b">
+      <c r="S147" t="n">
+        <v>1</v>
+      </c>
+      <c r="T147" t="n">
         <v>0</v>
       </c>
       <c r="U147" t="inlineStr">
@@ -12613,10 +12615,10 @@
       <c r="R148" t="n">
         <v>6</v>
       </c>
-      <c r="S148" t="b">
-        <v>1</v>
-      </c>
-      <c r="T148" t="b">
+      <c r="S148" t="n">
+        <v>1</v>
+      </c>
+      <c r="T148" t="n">
         <v>0</v>
       </c>
       <c r="U148" t="inlineStr">
@@ -12696,10 +12698,10 @@
       <c r="R149" t="n">
         <v>18</v>
       </c>
-      <c r="S149" t="b">
-        <v>1</v>
-      </c>
-      <c r="T149" t="b">
+      <c r="S149" t="n">
+        <v>1</v>
+      </c>
+      <c r="T149" t="n">
         <v>0</v>
       </c>
       <c r="U149" t="inlineStr">
@@ -12779,10 +12781,10 @@
       <c r="R150" t="n">
         <v>25</v>
       </c>
-      <c r="S150" t="b">
-        <v>1</v>
-      </c>
-      <c r="T150" t="b">
+      <c r="S150" t="n">
+        <v>1</v>
+      </c>
+      <c r="T150" t="n">
         <v>0</v>
       </c>
       <c r="U150" t="inlineStr">
@@ -12862,10 +12864,10 @@
       <c r="R151" t="n">
         <v>-2</v>
       </c>
-      <c r="S151" t="b">
-        <v>0</v>
-      </c>
-      <c r="T151" t="b">
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
         <v>1</v>
       </c>
       <c r="U151" t="inlineStr">
@@ -12945,10 +12947,10 @@
       <c r="R152" t="n">
         <v>14</v>
       </c>
-      <c r="S152" t="b">
-        <v>1</v>
-      </c>
-      <c r="T152" t="b">
+      <c r="S152" t="n">
+        <v>1</v>
+      </c>
+      <c r="T152" t="n">
         <v>0</v>
       </c>
       <c r="U152" t="inlineStr">
@@ -13028,10 +13030,10 @@
       <c r="R153" t="n">
         <v>22</v>
       </c>
-      <c r="S153" t="b">
-        <v>1</v>
-      </c>
-      <c r="T153" t="b">
+      <c r="S153" t="n">
+        <v>1</v>
+      </c>
+      <c r="T153" t="n">
         <v>0</v>
       </c>
       <c r="U153" t="inlineStr">
@@ -13111,10 +13113,10 @@
       <c r="R154" t="n">
         <v>11</v>
       </c>
-      <c r="S154" t="b">
-        <v>1</v>
-      </c>
-      <c r="T154" t="b">
+      <c r="S154" t="n">
+        <v>1</v>
+      </c>
+      <c r="T154" t="n">
         <v>0</v>
       </c>
       <c r="U154" t="inlineStr">
@@ -13194,10 +13196,10 @@
       <c r="R155" t="n">
         <v>36</v>
       </c>
-      <c r="S155" t="b">
-        <v>1</v>
-      </c>
-      <c r="T155" t="b">
+      <c r="S155" t="n">
+        <v>1</v>
+      </c>
+      <c r="T155" t="n">
         <v>0</v>
       </c>
       <c r="U155" t="inlineStr">
@@ -13277,10 +13279,10 @@
       <c r="R156" t="n">
         <v>-11</v>
       </c>
-      <c r="S156" t="b">
-        <v>0</v>
-      </c>
-      <c r="T156" t="b">
+      <c r="S156" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
         <v>1</v>
       </c>
       <c r="U156" t="inlineStr">
@@ -13360,10 +13362,10 @@
       <c r="R157" t="n">
         <v>-2</v>
       </c>
-      <c r="S157" t="b">
-        <v>0</v>
-      </c>
-      <c r="T157" t="b">
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
         <v>1</v>
       </c>
       <c r="U157" t="inlineStr">
@@ -13516,10 +13518,10 @@
       <c r="R159" t="n">
         <v>16</v>
       </c>
-      <c r="S159" t="b">
-        <v>1</v>
-      </c>
-      <c r="T159" t="b">
+      <c r="S159" t="n">
+        <v>1</v>
+      </c>
+      <c r="T159" t="n">
         <v>0</v>
       </c>
       <c r="U159" t="inlineStr">
@@ -13672,10 +13674,10 @@
       <c r="R161" t="n">
         <v>9</v>
       </c>
-      <c r="S161" t="b">
-        <v>1</v>
-      </c>
-      <c r="T161" t="b">
+      <c r="S161" t="n">
+        <v>1</v>
+      </c>
+      <c r="T161" t="n">
         <v>0</v>
       </c>
       <c r="U161" t="inlineStr">
@@ -13828,10 +13830,10 @@
       <c r="R163" t="n">
         <v>-12</v>
       </c>
-      <c r="S163" t="b">
-        <v>0</v>
-      </c>
-      <c r="T163" t="b">
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
         <v>1</v>
       </c>
       <c r="U163" t="inlineStr">
@@ -13911,10 +13913,10 @@
       <c r="R164" t="n">
         <v>7</v>
       </c>
-      <c r="S164" t="b">
-        <v>1</v>
-      </c>
-      <c r="T164" t="b">
+      <c r="S164" t="n">
+        <v>1</v>
+      </c>
+      <c r="T164" t="n">
         <v>0</v>
       </c>
       <c r="U164" t="inlineStr">
@@ -13994,10 +13996,10 @@
       <c r="R165" t="n">
         <v>4</v>
       </c>
-      <c r="S165" t="b">
-        <v>1</v>
-      </c>
-      <c r="T165" t="b">
+      <c r="S165" t="n">
+        <v>1</v>
+      </c>
+      <c r="T165" t="n">
         <v>0</v>
       </c>
       <c r="U165" t="inlineStr">
@@ -14077,10 +14079,10 @@
       <c r="R166" t="n">
         <v>15</v>
       </c>
-      <c r="S166" t="b">
-        <v>1</v>
-      </c>
-      <c r="T166" t="b">
+      <c r="S166" t="n">
+        <v>1</v>
+      </c>
+      <c r="T166" t="n">
         <v>0</v>
       </c>
       <c r="U166" t="inlineStr">
@@ -14160,10 +14162,10 @@
       <c r="R167" t="n">
         <v>3</v>
       </c>
-      <c r="S167" t="b">
-        <v>1</v>
-      </c>
-      <c r="T167" t="b">
+      <c r="S167" t="n">
+        <v>1</v>
+      </c>
+      <c r="T167" t="n">
         <v>0</v>
       </c>
       <c r="U167" t="inlineStr">
@@ -14243,10 +14245,10 @@
       <c r="R168" t="n">
         <v>2</v>
       </c>
-      <c r="S168" t="b">
-        <v>1</v>
-      </c>
-      <c r="T168" t="b">
+      <c r="S168" t="n">
+        <v>1</v>
+      </c>
+      <c r="T168" t="n">
         <v>0</v>
       </c>
       <c r="U168" t="inlineStr">
@@ -14326,10 +14328,10 @@
       <c r="R169" t="n">
         <v>-4</v>
       </c>
-      <c r="S169" t="b">
-        <v>0</v>
-      </c>
-      <c r="T169" t="b">
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
         <v>1</v>
       </c>
       <c r="U169" t="inlineStr">
@@ -14409,10 +14411,10 @@
       <c r="R170" t="n">
         <v>11</v>
       </c>
-      <c r="S170" t="b">
-        <v>1</v>
-      </c>
-      <c r="T170" t="b">
+      <c r="S170" t="n">
+        <v>1</v>
+      </c>
+      <c r="T170" t="n">
         <v>0</v>
       </c>
       <c r="U170" t="inlineStr">
@@ -14492,10 +14494,10 @@
       <c r="R171" t="n">
         <v>16</v>
       </c>
-      <c r="S171" t="b">
-        <v>1</v>
-      </c>
-      <c r="T171" t="b">
+      <c r="S171" t="n">
+        <v>1</v>
+      </c>
+      <c r="T171" t="n">
         <v>0</v>
       </c>
       <c r="U171" t="inlineStr">
@@ -14648,10 +14650,10 @@
       <c r="R173" t="n">
         <v>20</v>
       </c>
-      <c r="S173" t="b">
-        <v>1</v>
-      </c>
-      <c r="T173" t="b">
+      <c r="S173" t="n">
+        <v>1</v>
+      </c>
+      <c r="T173" t="n">
         <v>0</v>
       </c>
       <c r="U173" t="inlineStr">
@@ -14731,10 +14733,10 @@
       <c r="R174" t="n">
         <v>3</v>
       </c>
-      <c r="S174" t="b">
-        <v>1</v>
-      </c>
-      <c r="T174" t="b">
+      <c r="S174" t="n">
+        <v>1</v>
+      </c>
+      <c r="T174" t="n">
         <v>0</v>
       </c>
       <c r="U174" t="inlineStr">
@@ -14887,10 +14889,10 @@
       <c r="R176" t="n">
         <v>4</v>
       </c>
-      <c r="S176" t="b">
-        <v>1</v>
-      </c>
-      <c r="T176" t="b">
+      <c r="S176" t="n">
+        <v>1</v>
+      </c>
+      <c r="T176" t="n">
         <v>0</v>
       </c>
       <c r="U176" t="inlineStr">
@@ -14970,10 +14972,10 @@
       <c r="R177" t="n">
         <v>14</v>
       </c>
-      <c r="S177" t="b">
-        <v>1</v>
-      </c>
-      <c r="T177" t="b">
+      <c r="S177" t="n">
+        <v>1</v>
+      </c>
+      <c r="T177" t="n">
         <v>0</v>
       </c>
       <c r="U177" t="inlineStr">
@@ -15053,10 +15055,10 @@
       <c r="R178" t="n">
         <v>6</v>
       </c>
-      <c r="S178" t="b">
-        <v>1</v>
-      </c>
-      <c r="T178" t="b">
+      <c r="S178" t="n">
+        <v>1</v>
+      </c>
+      <c r="T178" t="n">
         <v>0</v>
       </c>
       <c r="U178" t="inlineStr">
@@ -15136,10 +15138,10 @@
       <c r="R179" t="n">
         <v>6</v>
       </c>
-      <c r="S179" t="b">
-        <v>1</v>
-      </c>
-      <c r="T179" t="b">
+      <c r="S179" t="n">
+        <v>1</v>
+      </c>
+      <c r="T179" t="n">
         <v>0</v>
       </c>
       <c r="U179" t="inlineStr">
@@ -15217,10 +15219,10 @@
       <c r="R180" t="n">
         <v>16</v>
       </c>
-      <c r="S180" t="b">
-        <v>1</v>
-      </c>
-      <c r="T180" t="b">
+      <c r="S180" t="n">
+        <v>1</v>
+      </c>
+      <c r="T180" t="n">
         <v>0</v>
       </c>
       <c r="U180" t="inlineStr">
@@ -15300,10 +15302,10 @@
       <c r="R181" t="n">
         <v>7</v>
       </c>
-      <c r="S181" t="b">
-        <v>1</v>
-      </c>
-      <c r="T181" t="b">
+      <c r="S181" t="n">
+        <v>1</v>
+      </c>
+      <c r="T181" t="n">
         <v>0</v>
       </c>
       <c r="U181" t="inlineStr">
@@ -15383,10 +15385,10 @@
       <c r="R182" t="n">
         <v>12</v>
       </c>
-      <c r="S182" t="b">
-        <v>1</v>
-      </c>
-      <c r="T182" t="b">
+      <c r="S182" t="n">
+        <v>1</v>
+      </c>
+      <c r="T182" t="n">
         <v>0</v>
       </c>
       <c r="U182" t="inlineStr">
@@ -15466,10 +15468,10 @@
       <c r="R183" t="n">
         <v>-2</v>
       </c>
-      <c r="S183" t="b">
-        <v>0</v>
-      </c>
-      <c r="T183" t="b">
+      <c r="S183" t="n">
+        <v>0</v>
+      </c>
+      <c r="T183" t="n">
         <v>1</v>
       </c>
       <c r="U183" t="inlineStr">
@@ -15549,10 +15551,10 @@
       <c r="R184" t="n">
         <v>-7</v>
       </c>
-      <c r="S184" t="b">
-        <v>0</v>
-      </c>
-      <c r="T184" t="b">
+      <c r="S184" t="n">
+        <v>0</v>
+      </c>
+      <c r="T184" t="n">
         <v>1</v>
       </c>
       <c r="U184" t="inlineStr">
@@ -15632,10 +15634,10 @@
       <c r="R185" t="n">
         <v>2</v>
       </c>
-      <c r="S185" t="b">
-        <v>1</v>
-      </c>
-      <c r="T185" t="b">
+      <c r="S185" t="n">
+        <v>1</v>
+      </c>
+      <c r="T185" t="n">
         <v>0</v>
       </c>
       <c r="U185" t="inlineStr">
@@ -15715,10 +15717,10 @@
       <c r="R186" t="n">
         <v>0</v>
       </c>
-      <c r="S186" t="b">
-        <v>0</v>
-      </c>
-      <c r="T186" t="b">
+      <c r="S186" t="n">
+        <v>0</v>
+      </c>
+      <c r="T186" t="n">
         <v>0</v>
       </c>
       <c r="U186" t="inlineStr">
@@ -15798,10 +15800,10 @@
       <c r="R187" t="n">
         <v>-1</v>
       </c>
-      <c r="S187" t="b">
-        <v>0</v>
-      </c>
-      <c r="T187" t="b">
+      <c r="S187" t="n">
+        <v>0</v>
+      </c>
+      <c r="T187" t="n">
         <v>1</v>
       </c>
       <c r="U187" t="inlineStr">
@@ -15881,10 +15883,10 @@
       <c r="R188" t="n">
         <v>-12</v>
       </c>
-      <c r="S188" t="b">
-        <v>0</v>
-      </c>
-      <c r="T188" t="b">
+      <c r="S188" t="n">
+        <v>0</v>
+      </c>
+      <c r="T188" t="n">
         <v>1</v>
       </c>
       <c r="U188" t="inlineStr">
@@ -15964,10 +15966,10 @@
       <c r="R189" t="n">
         <v>-2</v>
       </c>
-      <c r="S189" t="b">
-        <v>0</v>
-      </c>
-      <c r="T189" t="b">
+      <c r="S189" t="n">
+        <v>0</v>
+      </c>
+      <c r="T189" t="n">
         <v>1</v>
       </c>
       <c r="U189" t="inlineStr">
@@ -16047,10 +16049,10 @@
       <c r="R190" t="n">
         <v>9</v>
       </c>
-      <c r="S190" t="b">
-        <v>1</v>
-      </c>
-      <c r="T190" t="b">
+      <c r="S190" t="n">
+        <v>1</v>
+      </c>
+      <c r="T190" t="n">
         <v>0</v>
       </c>
       <c r="U190" t="inlineStr">
@@ -16130,10 +16132,10 @@
       <c r="R191" t="n">
         <v>28</v>
       </c>
-      <c r="S191" t="b">
-        <v>1</v>
-      </c>
-      <c r="T191" t="b">
+      <c r="S191" t="n">
+        <v>1</v>
+      </c>
+      <c r="T191" t="n">
         <v>0</v>
       </c>
       <c r="U191" t="inlineStr">
@@ -16286,10 +16288,10 @@
       <c r="R193" t="n">
         <v>17</v>
       </c>
-      <c r="S193" t="b">
-        <v>1</v>
-      </c>
-      <c r="T193" t="b">
+      <c r="S193" t="n">
+        <v>1</v>
+      </c>
+      <c r="T193" t="n">
         <v>0</v>
       </c>
       <c r="U193" t="inlineStr">
@@ -16442,10 +16444,10 @@
       <c r="R195" t="n">
         <v>7</v>
       </c>
-      <c r="S195" t="b">
-        <v>1</v>
-      </c>
-      <c r="T195" t="b">
+      <c r="S195" t="n">
+        <v>1</v>
+      </c>
+      <c r="T195" t="n">
         <v>0</v>
       </c>
       <c r="U195" t="inlineStr">
@@ -16525,10 +16527,10 @@
       <c r="R196" t="n">
         <v>7</v>
       </c>
-      <c r="S196" t="b">
-        <v>1</v>
-      </c>
-      <c r="T196" t="b">
+      <c r="S196" t="n">
+        <v>1</v>
+      </c>
+      <c r="T196" t="n">
         <v>0</v>
       </c>
       <c r="U196" t="inlineStr">
@@ -16608,10 +16610,10 @@
       <c r="R197" t="n">
         <v>-8</v>
       </c>
-      <c r="S197" t="b">
-        <v>0</v>
-      </c>
-      <c r="T197" t="b">
+      <c r="S197" t="n">
+        <v>0</v>
+      </c>
+      <c r="T197" t="n">
         <v>1</v>
       </c>
       <c r="U197" t="inlineStr">
@@ -16691,10 +16693,10 @@
       <c r="R198" t="n">
         <v>12</v>
       </c>
-      <c r="S198" t="b">
-        <v>1</v>
-      </c>
-      <c r="T198" t="b">
+      <c r="S198" t="n">
+        <v>1</v>
+      </c>
+      <c r="T198" t="n">
         <v>0</v>
       </c>
       <c r="U198" t="inlineStr">
@@ -16774,10 +16776,10 @@
       <c r="R199" t="n">
         <v>24</v>
       </c>
-      <c r="S199" t="b">
-        <v>1</v>
-      </c>
-      <c r="T199" t="b">
+      <c r="S199" t="n">
+        <v>1</v>
+      </c>
+      <c r="T199" t="n">
         <v>0</v>
       </c>
       <c r="U199" t="inlineStr">
@@ -16857,10 +16859,10 @@
       <c r="R200" t="n">
         <v>1</v>
       </c>
-      <c r="S200" t="b">
-        <v>1</v>
-      </c>
-      <c r="T200" t="b">
+      <c r="S200" t="n">
+        <v>1</v>
+      </c>
+      <c r="T200" t="n">
         <v>0</v>
       </c>
       <c r="U200" t="inlineStr">
@@ -16940,10 +16942,10 @@
       <c r="R201" t="n">
         <v>-5</v>
       </c>
-      <c r="S201" t="b">
-        <v>0</v>
-      </c>
-      <c r="T201" t="b">
+      <c r="S201" t="n">
+        <v>0</v>
+      </c>
+      <c r="T201" t="n">
         <v>1</v>
       </c>
       <c r="U201" t="inlineStr">
@@ -17023,10 +17025,10 @@
       <c r="R202" t="n">
         <v>-4</v>
       </c>
-      <c r="S202" t="b">
-        <v>0</v>
-      </c>
-      <c r="T202" t="b">
+      <c r="S202" t="n">
+        <v>0</v>
+      </c>
+      <c r="T202" t="n">
         <v>1</v>
       </c>
       <c r="U202" t="inlineStr">
@@ -17106,10 +17108,10 @@
       <c r="R203" t="n">
         <v>-6</v>
       </c>
-      <c r="S203" t="b">
-        <v>0</v>
-      </c>
-      <c r="T203" t="b">
+      <c r="S203" t="n">
+        <v>0</v>
+      </c>
+      <c r="T203" t="n">
         <v>1</v>
       </c>
       <c r="U203" t="inlineStr">
@@ -17189,10 +17191,10 @@
       <c r="R204" t="n">
         <v>4</v>
       </c>
-      <c r="S204" t="b">
-        <v>1</v>
-      </c>
-      <c r="T204" t="b">
+      <c r="S204" t="n">
+        <v>1</v>
+      </c>
+      <c r="T204" t="n">
         <v>0</v>
       </c>
       <c r="U204" t="inlineStr">
@@ -17272,10 +17274,10 @@
       <c r="R205" t="n">
         <v>8</v>
       </c>
-      <c r="S205" t="b">
-        <v>1</v>
-      </c>
-      <c r="T205" t="b">
+      <c r="S205" t="n">
+        <v>1</v>
+      </c>
+      <c r="T205" t="n">
         <v>0</v>
       </c>
       <c r="U205" t="inlineStr">
@@ -17355,10 +17357,10 @@
       <c r="R206" t="n">
         <v>-7</v>
       </c>
-      <c r="S206" t="b">
-        <v>0</v>
-      </c>
-      <c r="T206" t="b">
+      <c r="S206" t="n">
+        <v>0</v>
+      </c>
+      <c r="T206" t="n">
         <v>1</v>
       </c>
       <c r="U206" t="inlineStr">
@@ -17438,10 +17440,10 @@
       <c r="R207" t="n">
         <v>12</v>
       </c>
-      <c r="S207" t="b">
-        <v>1</v>
-      </c>
-      <c r="T207" t="b">
+      <c r="S207" t="n">
+        <v>1</v>
+      </c>
+      <c r="T207" t="n">
         <v>0</v>
       </c>
       <c r="U207" t="inlineStr">
@@ -17521,10 +17523,10 @@
       <c r="R208" t="n">
         <v>-7</v>
       </c>
-      <c r="S208" t="b">
-        <v>0</v>
-      </c>
-      <c r="T208" t="b">
+      <c r="S208" t="n">
+        <v>0</v>
+      </c>
+      <c r="T208" t="n">
         <v>1</v>
       </c>
       <c r="U208" t="inlineStr">
@@ -17604,10 +17606,10 @@
       <c r="R209" t="n">
         <v>19</v>
       </c>
-      <c r="S209" t="b">
-        <v>1</v>
-      </c>
-      <c r="T209" t="b">
+      <c r="S209" t="n">
+        <v>1</v>
+      </c>
+      <c r="T209" t="n">
         <v>0</v>
       </c>
       <c r="U209" t="inlineStr">
@@ -17687,10 +17689,10 @@
       <c r="R210" t="n">
         <v>13</v>
       </c>
-      <c r="S210" t="b">
-        <v>1</v>
-      </c>
-      <c r="T210" t="b">
+      <c r="S210" t="n">
+        <v>1</v>
+      </c>
+      <c r="T210" t="n">
         <v>0</v>
       </c>
       <c r="U210" t="inlineStr">
@@ -17770,10 +17772,10 @@
       <c r="R211" t="n">
         <v>7</v>
       </c>
-      <c r="S211" t="b">
-        <v>1</v>
-      </c>
-      <c r="T211" t="b">
+      <c r="S211" t="n">
+        <v>1</v>
+      </c>
+      <c r="T211" t="n">
         <v>0</v>
       </c>
       <c r="U211" t="inlineStr">
@@ -17853,10 +17855,10 @@
       <c r="R212" t="n">
         <v>-4</v>
       </c>
-      <c r="S212" t="b">
-        <v>0</v>
-      </c>
-      <c r="T212" t="b">
+      <c r="S212" t="n">
+        <v>0</v>
+      </c>
+      <c r="T212" t="n">
         <v>1</v>
       </c>
       <c r="U212" t="inlineStr">
@@ -17936,10 +17938,10 @@
       <c r="R213" t="n">
         <v>28</v>
       </c>
-      <c r="S213" t="b">
-        <v>1</v>
-      </c>
-      <c r="T213" t="b">
+      <c r="S213" t="n">
+        <v>1</v>
+      </c>
+      <c r="T213" t="n">
         <v>0</v>
       </c>
       <c r="U213" t="inlineStr">
@@ -18019,10 +18021,10 @@
       <c r="R214" t="n">
         <v>-5</v>
       </c>
-      <c r="S214" t="b">
-        <v>0</v>
-      </c>
-      <c r="T214" t="b">
+      <c r="S214" t="n">
+        <v>0</v>
+      </c>
+      <c r="T214" t="n">
         <v>1</v>
       </c>
       <c r="U214" t="inlineStr">
@@ -18102,10 +18104,10 @@
       <c r="R215" t="n">
         <v>1</v>
       </c>
-      <c r="S215" t="b">
-        <v>1</v>
-      </c>
-      <c r="T215" t="b">
+      <c r="S215" t="n">
+        <v>1</v>
+      </c>
+      <c r="T215" t="n">
         <v>0</v>
       </c>
       <c r="U215" t="inlineStr">
@@ -18183,10 +18185,10 @@
       <c r="R216" t="n">
         <v>5</v>
       </c>
-      <c r="S216" t="b">
-        <v>1</v>
-      </c>
-      <c r="T216" t="b">
+      <c r="S216" t="n">
+        <v>1</v>
+      </c>
+      <c r="T216" t="n">
         <v>0</v>
       </c>
       <c r="U216" t="inlineStr">
@@ -18266,10 +18268,10 @@
       <c r="R217" t="n">
         <v>7</v>
       </c>
-      <c r="S217" t="b">
-        <v>1</v>
-      </c>
-      <c r="T217" t="b">
+      <c r="S217" t="n">
+        <v>1</v>
+      </c>
+      <c r="T217" t="n">
         <v>0</v>
       </c>
       <c r="U217" t="inlineStr">
@@ -18349,10 +18351,10 @@
       <c r="R218" t="n">
         <v>3</v>
       </c>
-      <c r="S218" t="b">
-        <v>1</v>
-      </c>
-      <c r="T218" t="b">
+      <c r="S218" t="n">
+        <v>1</v>
+      </c>
+      <c r="T218" t="n">
         <v>0</v>
       </c>
       <c r="U218" t="inlineStr">
@@ -18432,10 +18434,10 @@
       <c r="R219" t="n">
         <v>8</v>
       </c>
-      <c r="S219" t="b">
-        <v>1</v>
-      </c>
-      <c r="T219" t="b">
+      <c r="S219" t="n">
+        <v>1</v>
+      </c>
+      <c r="T219" t="n">
         <v>0</v>
       </c>
       <c r="U219" t="inlineStr">
@@ -18513,10 +18515,10 @@
       <c r="R220" t="n">
         <v>-2</v>
       </c>
-      <c r="S220" t="b">
-        <v>0</v>
-      </c>
-      <c r="T220" t="b">
+      <c r="S220" t="n">
+        <v>0</v>
+      </c>
+      <c r="T220" t="n">
         <v>1</v>
       </c>
       <c r="U220" t="inlineStr">
@@ -18596,10 +18598,10 @@
       <c r="R221" t="n">
         <v>14</v>
       </c>
-      <c r="S221" t="b">
-        <v>1</v>
-      </c>
-      <c r="T221" t="b">
+      <c r="S221" t="n">
+        <v>1</v>
+      </c>
+      <c r="T221" t="n">
         <v>0</v>
       </c>
       <c r="U221" t="inlineStr">
@@ -18679,10 +18681,10 @@
       <c r="R222" t="n">
         <v>-2</v>
       </c>
-      <c r="S222" t="b">
-        <v>0</v>
-      </c>
-      <c r="T222" t="b">
+      <c r="S222" t="n">
+        <v>0</v>
+      </c>
+      <c r="T222" t="n">
         <v>1</v>
       </c>
       <c r="U222" t="inlineStr">
@@ -18762,10 +18764,10 @@
       <c r="R223" t="n">
         <v>8</v>
       </c>
-      <c r="S223" t="b">
-        <v>1</v>
-      </c>
-      <c r="T223" t="b">
+      <c r="S223" t="n">
+        <v>1</v>
+      </c>
+      <c r="T223" t="n">
         <v>0</v>
       </c>
       <c r="U223" t="inlineStr">
@@ -18845,10 +18847,10 @@
       <c r="R224" t="n">
         <v>-4</v>
       </c>
-      <c r="S224" t="b">
-        <v>0</v>
-      </c>
-      <c r="T224" t="b">
+      <c r="S224" t="n">
+        <v>0</v>
+      </c>
+      <c r="T224" t="n">
         <v>1</v>
       </c>
       <c r="U224" t="inlineStr">
@@ -18928,10 +18930,10 @@
       <c r="R225" t="n">
         <v>4</v>
       </c>
-      <c r="S225" t="b">
-        <v>1</v>
-      </c>
-      <c r="T225" t="b">
+      <c r="S225" t="n">
+        <v>1</v>
+      </c>
+      <c r="T225" t="n">
         <v>0</v>
       </c>
       <c r="U225" t="inlineStr">
@@ -19011,10 +19013,10 @@
       <c r="R226" t="n">
         <v>37</v>
       </c>
-      <c r="S226" t="b">
-        <v>1</v>
-      </c>
-      <c r="T226" t="b">
+      <c r="S226" t="n">
+        <v>1</v>
+      </c>
+      <c r="T226" t="n">
         <v>0</v>
       </c>
       <c r="U226" t="inlineStr">
@@ -19094,10 +19096,10 @@
       <c r="R227" t="n">
         <v>-2</v>
       </c>
-      <c r="S227" t="b">
-        <v>0</v>
-      </c>
-      <c r="T227" t="b">
+      <c r="S227" t="n">
+        <v>0</v>
+      </c>
+      <c r="T227" t="n">
         <v>1</v>
       </c>
       <c r="U227" t="inlineStr">
@@ -19177,10 +19179,10 @@
       <c r="R228" t="n">
         <v>-8</v>
       </c>
-      <c r="S228" t="b">
-        <v>0</v>
-      </c>
-      <c r="T228" t="b">
+      <c r="S228" t="n">
+        <v>0</v>
+      </c>
+      <c r="T228" t="n">
         <v>1</v>
       </c>
       <c r="U228" t="inlineStr">
@@ -19260,10 +19262,10 @@
       <c r="R229" t="n">
         <v>19</v>
       </c>
-      <c r="S229" t="b">
-        <v>1</v>
-      </c>
-      <c r="T229" t="b">
+      <c r="S229" t="n">
+        <v>1</v>
+      </c>
+      <c r="T229" t="n">
         <v>0</v>
       </c>
       <c r="U229" t="inlineStr">
@@ -19343,10 +19345,10 @@
       <c r="R230" t="n">
         <v>9</v>
       </c>
-      <c r="S230" t="b">
-        <v>1</v>
-      </c>
-      <c r="T230" t="b">
+      <c r="S230" t="n">
+        <v>1</v>
+      </c>
+      <c r="T230" t="n">
         <v>0</v>
       </c>
       <c r="U230" t="inlineStr">
@@ -19426,10 +19428,10 @@
       <c r="R231" t="n">
         <v>-6</v>
       </c>
-      <c r="S231" t="b">
-        <v>0</v>
-      </c>
-      <c r="T231" t="b">
+      <c r="S231" t="n">
+        <v>0</v>
+      </c>
+      <c r="T231" t="n">
         <v>1</v>
       </c>
       <c r="U231" t="inlineStr">
@@ -19509,10 +19511,10 @@
       <c r="R232" t="n">
         <v>22</v>
       </c>
-      <c r="S232" t="b">
-        <v>1</v>
-      </c>
-      <c r="T232" t="b">
+      <c r="S232" t="n">
+        <v>1</v>
+      </c>
+      <c r="T232" t="n">
         <v>0</v>
       </c>
       <c r="U232" t="inlineStr">
@@ -19592,10 +19594,10 @@
       <c r="R233" t="n">
         <v>17</v>
       </c>
-      <c r="S233" t="b">
-        <v>1</v>
-      </c>
-      <c r="T233" t="b">
+      <c r="S233" t="n">
+        <v>1</v>
+      </c>
+      <c r="T233" t="n">
         <v>0</v>
       </c>
       <c r="U233" t="inlineStr">
@@ -19675,10 +19677,10 @@
       <c r="R234" t="n">
         <v>17</v>
       </c>
-      <c r="S234" t="b">
-        <v>1</v>
-      </c>
-      <c r="T234" t="b">
+      <c r="S234" t="n">
+        <v>1</v>
+      </c>
+      <c r="T234" t="n">
         <v>0</v>
       </c>
       <c r="U234" t="inlineStr">
@@ -19758,10 +19760,10 @@
       <c r="R235" t="n">
         <v>36</v>
       </c>
-      <c r="S235" t="b">
-        <v>1</v>
-      </c>
-      <c r="T235" t="b">
+      <c r="S235" t="n">
+        <v>1</v>
+      </c>
+      <c r="T235" t="n">
         <v>0</v>
       </c>
       <c r="U235" t="inlineStr">
@@ -19841,10 +19843,10 @@
       <c r="R236" t="n">
         <v>2</v>
       </c>
-      <c r="S236" t="b">
-        <v>1</v>
-      </c>
-      <c r="T236" t="b">
+      <c r="S236" t="n">
+        <v>1</v>
+      </c>
+      <c r="T236" t="n">
         <v>0</v>
       </c>
       <c r="U236" t="inlineStr">
@@ -19924,10 +19926,10 @@
       <c r="R237" t="n">
         <v>9</v>
       </c>
-      <c r="S237" t="b">
-        <v>1</v>
-      </c>
-      <c r="T237" t="b">
+      <c r="S237" t="n">
+        <v>1</v>
+      </c>
+      <c r="T237" t="n">
         <v>0</v>
       </c>
       <c r="U237" t="inlineStr">
@@ -20007,10 +20009,10 @@
       <c r="R238" t="n">
         <v>-2</v>
       </c>
-      <c r="S238" t="b">
-        <v>0</v>
-      </c>
-      <c r="T238" t="b">
+      <c r="S238" t="n">
+        <v>0</v>
+      </c>
+      <c r="T238" t="n">
         <v>1</v>
       </c>
       <c r="U238" t="inlineStr">
@@ -20090,10 +20092,10 @@
       <c r="R239" t="n">
         <v>10</v>
       </c>
-      <c r="S239" t="b">
-        <v>1</v>
-      </c>
-      <c r="T239" t="b">
+      <c r="S239" t="n">
+        <v>1</v>
+      </c>
+      <c r="T239" t="n">
         <v>0</v>
       </c>
       <c r="U239" t="inlineStr">
@@ -20173,10 +20175,10 @@
       <c r="R240" t="n">
         <v>5</v>
       </c>
-      <c r="S240" t="b">
-        <v>1</v>
-      </c>
-      <c r="T240" t="b">
+      <c r="S240" t="n">
+        <v>1</v>
+      </c>
+      <c r="T240" t="n">
         <v>0</v>
       </c>
       <c r="U240" t="inlineStr">
@@ -20256,10 +20258,10 @@
       <c r="R241" t="n">
         <v>-1</v>
       </c>
-      <c r="S241" t="b">
-        <v>0</v>
-      </c>
-      <c r="T241" t="b">
+      <c r="S241" t="n">
+        <v>0</v>
+      </c>
+      <c r="T241" t="n">
         <v>1</v>
       </c>
       <c r="U241" t="inlineStr">
@@ -20339,10 +20341,10 @@
       <c r="R242" t="n">
         <v>13</v>
       </c>
-      <c r="S242" t="b">
-        <v>1</v>
-      </c>
-      <c r="T242" t="b">
+      <c r="S242" t="n">
+        <v>1</v>
+      </c>
+      <c r="T242" t="n">
         <v>0</v>
       </c>
       <c r="U242" t="inlineStr">
@@ -20422,10 +20424,10 @@
       <c r="R243" t="n">
         <v>-3</v>
       </c>
-      <c r="S243" t="b">
-        <v>0</v>
-      </c>
-      <c r="T243" t="b">
+      <c r="S243" t="n">
+        <v>0</v>
+      </c>
+      <c r="T243" t="n">
         <v>1</v>
       </c>
       <c r="U243" t="inlineStr">
@@ -20505,10 +20507,10 @@
       <c r="R244" t="n">
         <v>-3</v>
       </c>
-      <c r="S244" t="b">
-        <v>0</v>
-      </c>
-      <c r="T244" t="b">
+      <c r="S244" t="n">
+        <v>0</v>
+      </c>
+      <c r="T244" t="n">
         <v>1</v>
       </c>
       <c r="U244" t="inlineStr">
@@ -20588,10 +20590,10 @@
       <c r="R245" t="n">
         <v>-17</v>
       </c>
-      <c r="S245" t="b">
-        <v>0</v>
-      </c>
-      <c r="T245" t="b">
+      <c r="S245" t="n">
+        <v>0</v>
+      </c>
+      <c r="T245" t="n">
         <v>1</v>
       </c>
       <c r="U245" t="inlineStr">
@@ -20671,10 +20673,10 @@
       <c r="R246" t="n">
         <v>22</v>
       </c>
-      <c r="S246" t="b">
-        <v>1</v>
-      </c>
-      <c r="T246" t="b">
+      <c r="S246" t="n">
+        <v>1</v>
+      </c>
+      <c r="T246" t="n">
         <v>0</v>
       </c>
       <c r="U246" t="inlineStr">
@@ -20754,10 +20756,10 @@
       <c r="R247" t="n">
         <v>7</v>
       </c>
-      <c r="S247" t="b">
-        <v>1</v>
-      </c>
-      <c r="T247" t="b">
+      <c r="S247" t="n">
+        <v>1</v>
+      </c>
+      <c r="T247" t="n">
         <v>0</v>
       </c>
       <c r="U247" t="inlineStr">
@@ -20837,10 +20839,10 @@
       <c r="R248" t="n">
         <v>-5</v>
       </c>
-      <c r="S248" t="b">
-        <v>0</v>
-      </c>
-      <c r="T248" t="b">
+      <c r="S248" t="n">
+        <v>0</v>
+      </c>
+      <c r="T248" t="n">
         <v>1</v>
       </c>
       <c r="U248" t="inlineStr">
@@ -20920,10 +20922,10 @@
       <c r="R249" t="n">
         <v>19</v>
       </c>
-      <c r="S249" t="b">
-        <v>1</v>
-      </c>
-      <c r="T249" t="b">
+      <c r="S249" t="n">
+        <v>1</v>
+      </c>
+      <c r="T249" t="n">
         <v>0</v>
       </c>
       <c r="U249" t="inlineStr">
@@ -21003,10 +21005,10 @@
       <c r="R250" t="n">
         <v>-5</v>
       </c>
-      <c r="S250" t="b">
-        <v>0</v>
-      </c>
-      <c r="T250" t="b">
+      <c r="S250" t="n">
+        <v>0</v>
+      </c>
+      <c r="T250" t="n">
         <v>1</v>
       </c>
       <c r="U250" t="inlineStr">
@@ -21086,10 +21088,10 @@
       <c r="R251" t="n">
         <v>7</v>
       </c>
-      <c r="S251" t="b">
-        <v>1</v>
-      </c>
-      <c r="T251" t="b">
+      <c r="S251" t="n">
+        <v>1</v>
+      </c>
+      <c r="T251" t="n">
         <v>0</v>
       </c>
       <c r="U251" t="inlineStr">
@@ -21169,10 +21171,10 @@
       <c r="R252" t="n">
         <v>14</v>
       </c>
-      <c r="S252" t="b">
-        <v>1</v>
-      </c>
-      <c r="T252" t="b">
+      <c r="S252" t="n">
+        <v>1</v>
+      </c>
+      <c r="T252" t="n">
         <v>0</v>
       </c>
       <c r="U252" t="inlineStr">
@@ -21252,10 +21254,10 @@
       <c r="R253" t="n">
         <v>-1</v>
       </c>
-      <c r="S253" t="b">
-        <v>0</v>
-      </c>
-      <c r="T253" t="b">
+      <c r="S253" t="n">
+        <v>0</v>
+      </c>
+      <c r="T253" t="n">
         <v>1</v>
       </c>
       <c r="U253" t="inlineStr">
@@ -21335,10 +21337,10 @@
       <c r="R254" t="n">
         <v>15</v>
       </c>
-      <c r="S254" t="b">
-        <v>1</v>
-      </c>
-      <c r="T254" t="b">
+      <c r="S254" t="n">
+        <v>1</v>
+      </c>
+      <c r="T254" t="n">
         <v>0</v>
       </c>
       <c r="U254" t="inlineStr">
@@ -21418,10 +21420,10 @@
       <c r="R255" t="n">
         <v>11</v>
       </c>
-      <c r="S255" t="b">
-        <v>1</v>
-      </c>
-      <c r="T255" t="b">
+      <c r="S255" t="n">
+        <v>1</v>
+      </c>
+      <c r="T255" t="n">
         <v>0</v>
       </c>
       <c r="U255" t="inlineStr">
@@ -21501,10 +21503,10 @@
       <c r="R256" t="n">
         <v>13</v>
       </c>
-      <c r="S256" t="b">
-        <v>1</v>
-      </c>
-      <c r="T256" t="b">
+      <c r="S256" t="n">
+        <v>1</v>
+      </c>
+      <c r="T256" t="n">
         <v>0</v>
       </c>
       <c r="U256" t="inlineStr">
@@ -21584,10 +21586,10 @@
       <c r="R257" t="n">
         <v>-11</v>
       </c>
-      <c r="S257" t="b">
-        <v>0</v>
-      </c>
-      <c r="T257" t="b">
+      <c r="S257" t="n">
+        <v>0</v>
+      </c>
+      <c r="T257" t="n">
         <v>1</v>
       </c>
       <c r="U257" t="inlineStr">
@@ -21667,10 +21669,10 @@
       <c r="R258" t="n">
         <v>-3</v>
       </c>
-      <c r="S258" t="b">
-        <v>0</v>
-      </c>
-      <c r="T258" t="b">
+      <c r="S258" t="n">
+        <v>0</v>
+      </c>
+      <c r="T258" t="n">
         <v>1</v>
       </c>
       <c r="U258" t="inlineStr">
@@ -21750,10 +21752,10 @@
       <c r="R259" t="n">
         <v>28</v>
       </c>
-      <c r="S259" t="b">
-        <v>1</v>
-      </c>
-      <c r="T259" t="b">
+      <c r="S259" t="n">
+        <v>1</v>
+      </c>
+      <c r="T259" t="n">
         <v>0</v>
       </c>
       <c r="U259" t="inlineStr">
@@ -21833,10 +21835,10 @@
       <c r="R260" t="n">
         <v>0</v>
       </c>
-      <c r="S260" t="b">
-        <v>0</v>
-      </c>
-      <c r="T260" t="b">
+      <c r="S260" t="n">
+        <v>0</v>
+      </c>
+      <c r="T260" t="n">
         <v>0</v>
       </c>
       <c r="U260" t="inlineStr">
@@ -21916,10 +21918,10 @@
       <c r="R261" t="n">
         <v>2</v>
       </c>
-      <c r="S261" t="b">
-        <v>1</v>
-      </c>
-      <c r="T261" t="b">
+      <c r="S261" t="n">
+        <v>1</v>
+      </c>
+      <c r="T261" t="n">
         <v>0</v>
       </c>
       <c r="U261" t="inlineStr">
@@ -21999,10 +22001,10 @@
       <c r="R262" t="n">
         <v>5</v>
       </c>
-      <c r="S262" t="b">
-        <v>1</v>
-      </c>
-      <c r="T262" t="b">
+      <c r="S262" t="n">
+        <v>1</v>
+      </c>
+      <c r="T262" t="n">
         <v>0</v>
       </c>
       <c r="U262" t="inlineStr">
@@ -22082,10 +22084,10 @@
       <c r="R263" t="n">
         <v>17</v>
       </c>
-      <c r="S263" t="b">
-        <v>1</v>
-      </c>
-      <c r="T263" t="b">
+      <c r="S263" t="n">
+        <v>1</v>
+      </c>
+      <c r="T263" t="n">
         <v>0</v>
       </c>
       <c r="U263" t="inlineStr">
@@ -22165,10 +22167,10 @@
       <c r="R264" t="n">
         <v>0</v>
       </c>
-      <c r="S264" t="b">
-        <v>0</v>
-      </c>
-      <c r="T264" t="b">
+      <c r="S264" t="n">
+        <v>0</v>
+      </c>
+      <c r="T264" t="n">
         <v>0</v>
       </c>
       <c r="U264" t="inlineStr">
@@ -22246,10 +22248,10 @@
       <c r="R265" t="n">
         <v>7</v>
       </c>
-      <c r="S265" t="b">
-        <v>1</v>
-      </c>
-      <c r="T265" t="b">
+      <c r="S265" t="n">
+        <v>1</v>
+      </c>
+      <c r="T265" t="n">
         <v>0</v>
       </c>
       <c r="U265" t="inlineStr">
@@ -22329,10 +22331,10 @@
       <c r="R266" t="n">
         <v>11</v>
       </c>
-      <c r="S266" t="b">
-        <v>1</v>
-      </c>
-      <c r="T266" t="b">
+      <c r="S266" t="n">
+        <v>1</v>
+      </c>
+      <c r="T266" t="n">
         <v>0</v>
       </c>
       <c r="U266" t="inlineStr">
@@ -22412,10 +22414,10 @@
       <c r="R267" t="n">
         <v>9</v>
       </c>
-      <c r="S267" t="b">
-        <v>1</v>
-      </c>
-      <c r="T267" t="b">
+      <c r="S267" t="n">
+        <v>1</v>
+      </c>
+      <c r="T267" t="n">
         <v>0</v>
       </c>
       <c r="U267" t="inlineStr">
@@ -22495,10 +22497,10 @@
       <c r="R268" t="n">
         <v>31</v>
       </c>
-      <c r="S268" t="b">
-        <v>1</v>
-      </c>
-      <c r="T268" t="b">
+      <c r="S268" t="n">
+        <v>1</v>
+      </c>
+      <c r="T268" t="n">
         <v>0</v>
       </c>
       <c r="U268" t="inlineStr">
@@ -22578,10 +22580,10 @@
       <c r="R269" t="n">
         <v>9</v>
       </c>
-      <c r="S269" t="b">
-        <v>1</v>
-      </c>
-      <c r="T269" t="b">
+      <c r="S269" t="n">
+        <v>1</v>
+      </c>
+      <c r="T269" t="n">
         <v>0</v>
       </c>
       <c r="U269" t="inlineStr">
@@ -22661,10 +22663,10 @@
       <c r="R270" t="n">
         <v>-5</v>
       </c>
-      <c r="S270" t="b">
-        <v>0</v>
-      </c>
-      <c r="T270" t="b">
+      <c r="S270" t="n">
+        <v>0</v>
+      </c>
+      <c r="T270" t="n">
         <v>1</v>
       </c>
       <c r="U270" t="inlineStr">
@@ -22744,10 +22746,10 @@
       <c r="R271" t="n">
         <v>12</v>
       </c>
-      <c r="S271" t="b">
-        <v>1</v>
-      </c>
-      <c r="T271" t="b">
+      <c r="S271" t="n">
+        <v>1</v>
+      </c>
+      <c r="T271" t="n">
         <v>0</v>
       </c>
       <c r="U271" t="inlineStr">
@@ -22827,10 +22829,10 @@
       <c r="R272" t="n">
         <v>6</v>
       </c>
-      <c r="S272" t="b">
-        <v>1</v>
-      </c>
-      <c r="T272" t="b">
+      <c r="S272" t="n">
+        <v>1</v>
+      </c>
+      <c r="T272" t="n">
         <v>0</v>
       </c>
       <c r="U272" t="inlineStr">
@@ -22910,10 +22912,10 @@
       <c r="R273" t="n">
         <v>0</v>
       </c>
-      <c r="S273" t="b">
-        <v>0</v>
-      </c>
-      <c r="T273" t="b">
+      <c r="S273" t="n">
+        <v>0</v>
+      </c>
+      <c r="T273" t="n">
         <v>0</v>
       </c>
       <c r="U273" t="inlineStr">
@@ -22993,10 +22995,10 @@
       <c r="R274" t="n">
         <v>19</v>
       </c>
-      <c r="S274" t="b">
-        <v>1</v>
-      </c>
-      <c r="T274" t="b">
+      <c r="S274" t="n">
+        <v>1</v>
+      </c>
+      <c r="T274" t="n">
         <v>0</v>
       </c>
       <c r="U274" t="inlineStr">
@@ -23076,10 +23078,10 @@
       <c r="R275" t="n">
         <v>-5</v>
       </c>
-      <c r="S275" t="b">
-        <v>0</v>
-      </c>
-      <c r="T275" t="b">
+      <c r="S275" t="n">
+        <v>0</v>
+      </c>
+      <c r="T275" t="n">
         <v>1</v>
       </c>
       <c r="U275" t="inlineStr">
@@ -23159,10 +23161,10 @@
       <c r="R276" t="n">
         <v>1</v>
       </c>
-      <c r="S276" t="b">
-        <v>1</v>
-      </c>
-      <c r="T276" t="b">
+      <c r="S276" t="n">
+        <v>1</v>
+      </c>
+      <c r="T276" t="n">
         <v>0</v>
       </c>
       <c r="U276" t="inlineStr">
@@ -23242,10 +23244,10 @@
       <c r="R277" t="n">
         <v>9</v>
       </c>
-      <c r="S277" t="b">
-        <v>1</v>
-      </c>
-      <c r="T277" t="b">
+      <c r="S277" t="n">
+        <v>1</v>
+      </c>
+      <c r="T277" t="n">
         <v>0</v>
       </c>
       <c r="U277" t="inlineStr">
@@ -23325,10 +23327,10 @@
       <c r="R278" t="n">
         <v>-1</v>
       </c>
-      <c r="S278" t="b">
-        <v>0</v>
-      </c>
-      <c r="T278" t="b">
+      <c r="S278" t="n">
+        <v>0</v>
+      </c>
+      <c r="T278" t="n">
         <v>1</v>
       </c>
       <c r="U278" t="inlineStr">
@@ -23408,10 +23410,10 @@
       <c r="R279" t="n">
         <v>15</v>
       </c>
-      <c r="S279" t="b">
-        <v>1</v>
-      </c>
-      <c r="T279" t="b">
+      <c r="S279" t="n">
+        <v>1</v>
+      </c>
+      <c r="T279" t="n">
         <v>0</v>
       </c>
       <c r="U279" t="inlineStr">
@@ -23491,10 +23493,10 @@
       <c r="R280" t="n">
         <v>1</v>
       </c>
-      <c r="S280" t="b">
-        <v>1</v>
-      </c>
-      <c r="T280" t="b">
+      <c r="S280" t="n">
+        <v>1</v>
+      </c>
+      <c r="T280" t="n">
         <v>0</v>
       </c>
       <c r="U280" t="inlineStr">
@@ -23574,10 +23576,10 @@
       <c r="R281" t="n">
         <v>1</v>
       </c>
-      <c r="S281" t="b">
-        <v>1</v>
-      </c>
-      <c r="T281" t="b">
+      <c r="S281" t="n">
+        <v>1</v>
+      </c>
+      <c r="T281" t="n">
         <v>0</v>
       </c>
       <c r="U281" t="inlineStr">
@@ -23657,10 +23659,10 @@
       <c r="R282" t="n">
         <v>1</v>
       </c>
-      <c r="S282" t="b">
-        <v>1</v>
-      </c>
-      <c r="T282" t="b">
+      <c r="S282" t="n">
+        <v>1</v>
+      </c>
+      <c r="T282" t="n">
         <v>0</v>
       </c>
       <c r="U282" t="inlineStr">
@@ -23740,10 +23742,10 @@
       <c r="R283" t="n">
         <v>9</v>
       </c>
-      <c r="S283" t="b">
-        <v>1</v>
-      </c>
-      <c r="T283" t="b">
+      <c r="S283" t="n">
+        <v>1</v>
+      </c>
+      <c r="T283" t="n">
         <v>0</v>
       </c>
       <c r="U283" t="inlineStr">
@@ -23823,10 +23825,10 @@
       <c r="R284" t="n">
         <v>7</v>
       </c>
-      <c r="S284" t="b">
-        <v>1</v>
-      </c>
-      <c r="T284" t="b">
+      <c r="S284" t="n">
+        <v>1</v>
+      </c>
+      <c r="T284" t="n">
         <v>0</v>
       </c>
       <c r="U284" t="inlineStr">
@@ -23904,10 +23906,10 @@
       <c r="R285" t="n">
         <v>-1</v>
       </c>
-      <c r="S285" t="b">
-        <v>0</v>
-      </c>
-      <c r="T285" t="b">
+      <c r="S285" t="n">
+        <v>0</v>
+      </c>
+      <c r="T285" t="n">
         <v>1</v>
       </c>
       <c r="U285" t="inlineStr">
@@ -23987,10 +23989,10 @@
       <c r="R286" t="n">
         <v>-1</v>
       </c>
-      <c r="S286" t="b">
-        <v>0</v>
-      </c>
-      <c r="T286" t="b">
+      <c r="S286" t="n">
+        <v>0</v>
+      </c>
+      <c r="T286" t="n">
         <v>1</v>
       </c>
       <c r="U286" t="inlineStr">
@@ -24070,10 +24072,10 @@
       <c r="R287" t="n">
         <v>1</v>
       </c>
-      <c r="S287" t="b">
-        <v>1</v>
-      </c>
-      <c r="T287" t="b">
+      <c r="S287" t="n">
+        <v>1</v>
+      </c>
+      <c r="T287" t="n">
         <v>0</v>
       </c>
       <c r="U287" t="inlineStr">
@@ -24153,10 +24155,10 @@
       <c r="R288" t="n">
         <v>28</v>
       </c>
-      <c r="S288" t="b">
-        <v>1</v>
-      </c>
-      <c r="T288" t="b">
+      <c r="S288" t="n">
+        <v>1</v>
+      </c>
+      <c r="T288" t="n">
         <v>0</v>
       </c>
       <c r="U288" t="inlineStr">
@@ -24236,10 +24238,10 @@
       <c r="R289" t="n">
         <v>20</v>
       </c>
-      <c r="S289" t="b">
-        <v>1</v>
-      </c>
-      <c r="T289" t="b">
+      <c r="S289" t="n">
+        <v>1</v>
+      </c>
+      <c r="T289" t="n">
         <v>0</v>
       </c>
       <c r="U289" t="inlineStr">
@@ -24319,10 +24321,10 @@
       <c r="R290" t="n">
         <v>-5</v>
       </c>
-      <c r="S290" t="b">
-        <v>0</v>
-      </c>
-      <c r="T290" t="b">
+      <c r="S290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T290" t="n">
         <v>1</v>
       </c>
       <c r="U290" t="inlineStr">
@@ -24402,10 +24404,10 @@
       <c r="R291" t="n">
         <v>13</v>
       </c>
-      <c r="S291" t="b">
-        <v>1</v>
-      </c>
-      <c r="T291" t="b">
+      <c r="S291" t="n">
+        <v>1</v>
+      </c>
+      <c r="T291" t="n">
         <v>0</v>
       </c>
       <c r="U291" t="inlineStr">
@@ -24485,10 +24487,10 @@
       <c r="R292" t="n">
         <v>7</v>
       </c>
-      <c r="S292" t="b">
-        <v>1</v>
-      </c>
-      <c r="T292" t="b">
+      <c r="S292" t="n">
+        <v>1</v>
+      </c>
+      <c r="T292" t="n">
         <v>0</v>
       </c>
       <c r="U292" t="inlineStr">
@@ -24568,10 +24570,10 @@
       <c r="R293" t="n">
         <v>24</v>
       </c>
-      <c r="S293" t="b">
-        <v>1</v>
-      </c>
-      <c r="T293" t="b">
+      <c r="S293" t="n">
+        <v>1</v>
+      </c>
+      <c r="T293" t="n">
         <v>0</v>
       </c>
       <c r="U293" t="inlineStr">
@@ -24651,10 +24653,10 @@
       <c r="R294" t="n">
         <v>3</v>
       </c>
-      <c r="S294" t="b">
-        <v>1</v>
-      </c>
-      <c r="T294" t="b">
+      <c r="S294" t="n">
+        <v>1</v>
+      </c>
+      <c r="T294" t="n">
         <v>0</v>
       </c>
       <c r="U294" t="inlineStr">
@@ -24734,10 +24736,10 @@
       <c r="R295" t="n">
         <v>-12</v>
       </c>
-      <c r="S295" t="b">
-        <v>0</v>
-      </c>
-      <c r="T295" t="b">
+      <c r="S295" t="n">
+        <v>0</v>
+      </c>
+      <c r="T295" t="n">
         <v>1</v>
       </c>
       <c r="U295" t="inlineStr">
@@ -24817,10 +24819,10 @@
       <c r="R296" t="n">
         <v>12</v>
       </c>
-      <c r="S296" t="b">
-        <v>1</v>
-      </c>
-      <c r="T296" t="b">
+      <c r="S296" t="n">
+        <v>1</v>
+      </c>
+      <c r="T296" t="n">
         <v>0</v>
       </c>
       <c r="U296" t="inlineStr">
@@ -24900,10 +24902,10 @@
       <c r="R297" t="n">
         <v>-10</v>
       </c>
-      <c r="S297" t="b">
-        <v>0</v>
-      </c>
-      <c r="T297" t="b">
+      <c r="S297" t="n">
+        <v>0</v>
+      </c>
+      <c r="T297" t="n">
         <v>1</v>
       </c>
       <c r="U297" t="inlineStr">
@@ -24983,10 +24985,10 @@
       <c r="R298" t="n">
         <v>13</v>
       </c>
-      <c r="S298" t="b">
-        <v>1</v>
-      </c>
-      <c r="T298" t="b">
+      <c r="S298" t="n">
+        <v>1</v>
+      </c>
+      <c r="T298" t="n">
         <v>0</v>
       </c>
       <c r="U298" t="inlineStr">
@@ -25066,10 +25068,10 @@
       <c r="R299" t="n">
         <v>3</v>
       </c>
-      <c r="S299" t="b">
-        <v>1</v>
-      </c>
-      <c r="T299" t="b">
+      <c r="S299" t="n">
+        <v>1</v>
+      </c>
+      <c r="T299" t="n">
         <v>0</v>
       </c>
       <c r="U299" t="inlineStr">
@@ -25149,10 +25151,10 @@
       <c r="R300" t="n">
         <v>8</v>
       </c>
-      <c r="S300" t="b">
-        <v>1</v>
-      </c>
-      <c r="T300" t="b">
+      <c r="S300" t="n">
+        <v>1</v>
+      </c>
+      <c r="T300" t="n">
         <v>0</v>
       </c>
       <c r="U300" t="inlineStr">
@@ -25232,10 +25234,10 @@
       <c r="R301" t="n">
         <v>12</v>
       </c>
-      <c r="S301" t="b">
-        <v>1</v>
-      </c>
-      <c r="T301" t="b">
+      <c r="S301" t="n">
+        <v>1</v>
+      </c>
+      <c r="T301" t="n">
         <v>0</v>
       </c>
       <c r="U301" t="inlineStr">
@@ -25315,10 +25317,10 @@
       <c r="R302" t="n">
         <v>12</v>
       </c>
-      <c r="S302" t="b">
-        <v>1</v>
-      </c>
-      <c r="T302" t="b">
+      <c r="S302" t="n">
+        <v>1</v>
+      </c>
+      <c r="T302" t="n">
         <v>0</v>
       </c>
       <c r="U302" t="inlineStr">
@@ -25398,10 +25400,10 @@
       <c r="R303" t="n">
         <v>13</v>
       </c>
-      <c r="S303" t="b">
-        <v>1</v>
-      </c>
-      <c r="T303" t="b">
+      <c r="S303" t="n">
+        <v>1</v>
+      </c>
+      <c r="T303" t="n">
         <v>0</v>
       </c>
       <c r="U303" t="inlineStr">
@@ -25554,10 +25556,10 @@
       <c r="R305" t="n">
         <v>-21</v>
       </c>
-      <c r="S305" t="b">
-        <v>0</v>
-      </c>
-      <c r="T305" t="b">
+      <c r="S305" t="n">
+        <v>0</v>
+      </c>
+      <c r="T305" t="n">
         <v>1</v>
       </c>
       <c r="U305" t="inlineStr">
@@ -25637,10 +25639,10 @@
       <c r="R306" t="n">
         <v>-4</v>
       </c>
-      <c r="S306" t="b">
-        <v>0</v>
-      </c>
-      <c r="T306" t="b">
+      <c r="S306" t="n">
+        <v>0</v>
+      </c>
+      <c r="T306" t="n">
         <v>1</v>
       </c>
       <c r="U306" t="inlineStr">
@@ -25720,10 +25722,10 @@
       <c r="R307" t="n">
         <v>-11</v>
       </c>
-      <c r="S307" t="b">
-        <v>0</v>
-      </c>
-      <c r="T307" t="b">
+      <c r="S307" t="n">
+        <v>0</v>
+      </c>
+      <c r="T307" t="n">
         <v>1</v>
       </c>
       <c r="U307" t="inlineStr">
@@ -25803,10 +25805,10 @@
       <c r="R308" t="n">
         <v>-1</v>
       </c>
-      <c r="S308" t="b">
-        <v>0</v>
-      </c>
-      <c r="T308" t="b">
+      <c r="S308" t="n">
+        <v>0</v>
+      </c>
+      <c r="T308" t="n">
         <v>1</v>
       </c>
       <c r="U308" t="inlineStr">
@@ -25886,10 +25888,10 @@
       <c r="R309" t="n">
         <v>17</v>
       </c>
-      <c r="S309" t="b">
-        <v>1</v>
-      </c>
-      <c r="T309" t="b">
+      <c r="S309" t="n">
+        <v>1</v>
+      </c>
+      <c r="T309" t="n">
         <v>0</v>
       </c>
       <c r="U309" t="inlineStr">
@@ -25969,10 +25971,10 @@
       <c r="R310" t="n">
         <v>11</v>
       </c>
-      <c r="S310" t="b">
-        <v>1</v>
-      </c>
-      <c r="T310" t="b">
+      <c r="S310" t="n">
+        <v>1</v>
+      </c>
+      <c r="T310" t="n">
         <v>0</v>
       </c>
       <c r="U310" t="inlineStr">
@@ -26052,10 +26054,10 @@
       <c r="R311" t="n">
         <v>11</v>
       </c>
-      <c r="S311" t="b">
-        <v>1</v>
-      </c>
-      <c r="T311" t="b">
+      <c r="S311" t="n">
+        <v>1</v>
+      </c>
+      <c r="T311" t="n">
         <v>0</v>
       </c>
       <c r="U311" t="inlineStr">
@@ -26135,10 +26137,10 @@
       <c r="R312" t="n">
         <v>-2</v>
       </c>
-      <c r="S312" t="b">
-        <v>0</v>
-      </c>
-      <c r="T312" t="b">
+      <c r="S312" t="n">
+        <v>0</v>
+      </c>
+      <c r="T312" t="n">
         <v>1</v>
       </c>
       <c r="U312" t="inlineStr">
@@ -26218,10 +26220,10 @@
       <c r="R313" t="n">
         <v>17</v>
       </c>
-      <c r="S313" t="b">
-        <v>1</v>
-      </c>
-      <c r="T313" t="b">
+      <c r="S313" t="n">
+        <v>1</v>
+      </c>
+      <c r="T313" t="n">
         <v>0</v>
       </c>
       <c r="U313" t="inlineStr">
@@ -26301,10 +26303,10 @@
       <c r="R314" t="n">
         <v>4</v>
       </c>
-      <c r="S314" t="b">
-        <v>1</v>
-      </c>
-      <c r="T314" t="b">
+      <c r="S314" t="n">
+        <v>1</v>
+      </c>
+      <c r="T314" t="n">
         <v>0</v>
       </c>
       <c r="U314" t="inlineStr">
@@ -26384,10 +26386,10 @@
       <c r="R315" t="n">
         <v>9</v>
       </c>
-      <c r="S315" t="b">
-        <v>1</v>
-      </c>
-      <c r="T315" t="b">
+      <c r="S315" t="n">
+        <v>1</v>
+      </c>
+      <c r="T315" t="n">
         <v>0</v>
       </c>
       <c r="U315" t="inlineStr">
@@ -26467,10 +26469,10 @@
       <c r="R316" t="n">
         <v>7</v>
       </c>
-      <c r="S316" t="b">
-        <v>1</v>
-      </c>
-      <c r="T316" t="b">
+      <c r="S316" t="n">
+        <v>1</v>
+      </c>
+      <c r="T316" t="n">
         <v>0</v>
       </c>
       <c r="U316" t="inlineStr">
@@ -26550,10 +26552,10 @@
       <c r="R317" t="n">
         <v>13</v>
       </c>
-      <c r="S317" t="b">
-        <v>1</v>
-      </c>
-      <c r="T317" t="b">
+      <c r="S317" t="n">
+        <v>1</v>
+      </c>
+      <c r="T317" t="n">
         <v>0</v>
       </c>
       <c r="U317" t="inlineStr">
@@ -26633,10 +26635,10 @@
       <c r="R318" t="n">
         <v>3</v>
       </c>
-      <c r="S318" t="b">
-        <v>1</v>
-      </c>
-      <c r="T318" t="b">
+      <c r="S318" t="n">
+        <v>1</v>
+      </c>
+      <c r="T318" t="n">
         <v>0</v>
       </c>
       <c r="U318" t="inlineStr">
@@ -26716,10 +26718,10 @@
       <c r="R319" t="n">
         <v>8</v>
       </c>
-      <c r="S319" t="b">
-        <v>1</v>
-      </c>
-      <c r="T319" t="b">
+      <c r="S319" t="n">
+        <v>1</v>
+      </c>
+      <c r="T319" t="n">
         <v>0</v>
       </c>
       <c r="U319" t="inlineStr">
@@ -26872,10 +26874,10 @@
       <c r="R321" t="n">
         <v>-7</v>
       </c>
-      <c r="S321" t="b">
-        <v>0</v>
-      </c>
-      <c r="T321" t="b">
+      <c r="S321" t="n">
+        <v>0</v>
+      </c>
+      <c r="T321" t="n">
         <v>1</v>
       </c>
       <c r="U321" t="inlineStr">
@@ -26955,10 +26957,10 @@
       <c r="R322" t="n">
         <v>-2</v>
       </c>
-      <c r="S322" t="b">
-        <v>0</v>
-      </c>
-      <c r="T322" t="b">
+      <c r="S322" t="n">
+        <v>0</v>
+      </c>
+      <c r="T322" t="n">
         <v>1</v>
       </c>
       <c r="U322" t="inlineStr">
@@ -27038,10 +27040,10 @@
       <c r="R323" t="n">
         <v>4</v>
       </c>
-      <c r="S323" t="b">
-        <v>1</v>
-      </c>
-      <c r="T323" t="b">
+      <c r="S323" t="n">
+        <v>1</v>
+      </c>
+      <c r="T323" t="n">
         <v>0</v>
       </c>
       <c r="U323" t="inlineStr">
@@ -27121,10 +27123,10 @@
       <c r="R324" t="n">
         <v>-10</v>
       </c>
-      <c r="S324" t="b">
-        <v>0</v>
-      </c>
-      <c r="T324" t="b">
+      <c r="S324" t="n">
+        <v>0</v>
+      </c>
+      <c r="T324" t="n">
         <v>1</v>
       </c>
       <c r="U324" t="inlineStr">
@@ -27204,10 +27206,10 @@
       <c r="R325" t="n">
         <v>7</v>
       </c>
-      <c r="S325" t="b">
-        <v>1</v>
-      </c>
-      <c r="T325" t="b">
+      <c r="S325" t="n">
+        <v>1</v>
+      </c>
+      <c r="T325" t="n">
         <v>0</v>
       </c>
       <c r="U325" t="inlineStr">
@@ -27287,10 +27289,10 @@
       <c r="R326" t="n">
         <v>-8</v>
       </c>
-      <c r="S326" t="b">
-        <v>0</v>
-      </c>
-      <c r="T326" t="b">
+      <c r="S326" t="n">
+        <v>0</v>
+      </c>
+      <c r="T326" t="n">
         <v>1</v>
       </c>
       <c r="U326" t="inlineStr">
@@ -27370,10 +27372,10 @@
       <c r="R327" t="n">
         <v>15</v>
       </c>
-      <c r="S327" t="b">
-        <v>1</v>
-      </c>
-      <c r="T327" t="b">
+      <c r="S327" t="n">
+        <v>1</v>
+      </c>
+      <c r="T327" t="n">
         <v>0</v>
       </c>
       <c r="U327" t="inlineStr">
@@ -27453,10 +27455,10 @@
       <c r="R328" t="n">
         <v>-10</v>
       </c>
-      <c r="S328" t="b">
-        <v>0</v>
-      </c>
-      <c r="T328" t="b">
+      <c r="S328" t="n">
+        <v>0</v>
+      </c>
+      <c r="T328" t="n">
         <v>1</v>
       </c>
       <c r="U328" t="inlineStr">
@@ -27536,10 +27538,10 @@
       <c r="R329" t="n">
         <v>9</v>
       </c>
-      <c r="S329" t="b">
-        <v>1</v>
-      </c>
-      <c r="T329" t="b">
+      <c r="S329" t="n">
+        <v>1</v>
+      </c>
+      <c r="T329" t="n">
         <v>0</v>
       </c>
       <c r="U329" t="inlineStr">
@@ -27619,10 +27621,10 @@
       <c r="R330" t="n">
         <v>-10</v>
       </c>
-      <c r="S330" t="b">
-        <v>0</v>
-      </c>
-      <c r="T330" t="b">
+      <c r="S330" t="n">
+        <v>0</v>
+      </c>
+      <c r="T330" t="n">
         <v>1</v>
       </c>
       <c r="U330" t="inlineStr">
@@ -27702,10 +27704,10 @@
       <c r="R331" t="n">
         <v>14</v>
       </c>
-      <c r="S331" t="b">
-        <v>1</v>
-      </c>
-      <c r="T331" t="b">
+      <c r="S331" t="n">
+        <v>1</v>
+      </c>
+      <c r="T331" t="n">
         <v>0</v>
       </c>
       <c r="U331" t="inlineStr">
@@ -27785,10 +27787,10 @@
       <c r="R332" t="n">
         <v>8</v>
       </c>
-      <c r="S332" t="b">
-        <v>1</v>
-      </c>
-      <c r="T332" t="b">
+      <c r="S332" t="n">
+        <v>1</v>
+      </c>
+      <c r="T332" t="n">
         <v>0</v>
       </c>
       <c r="U332" t="inlineStr">
@@ -27868,10 +27870,10 @@
       <c r="R333" t="n">
         <v>-6</v>
       </c>
-      <c r="S333" t="b">
-        <v>0</v>
-      </c>
-      <c r="T333" t="b">
+      <c r="S333" t="n">
+        <v>0</v>
+      </c>
+      <c r="T333" t="n">
         <v>1</v>
       </c>
       <c r="U333" t="inlineStr">
@@ -27951,10 +27953,10 @@
       <c r="R334" t="n">
         <v>11</v>
       </c>
-      <c r="S334" t="b">
-        <v>1</v>
-      </c>
-      <c r="T334" t="b">
+      <c r="S334" t="n">
+        <v>1</v>
+      </c>
+      <c r="T334" t="n">
         <v>0</v>
       </c>
       <c r="U334" t="inlineStr">
@@ -28034,10 +28036,10 @@
       <c r="R335" t="n">
         <v>-2</v>
       </c>
-      <c r="S335" t="b">
-        <v>0</v>
-      </c>
-      <c r="T335" t="b">
+      <c r="S335" t="n">
+        <v>0</v>
+      </c>
+      <c r="T335" t="n">
         <v>1</v>
       </c>
       <c r="U335" t="inlineStr">
@@ -28117,10 +28119,10 @@
       <c r="R336" t="n">
         <v>-12</v>
       </c>
-      <c r="S336" t="b">
-        <v>0</v>
-      </c>
-      <c r="T336" t="b">
+      <c r="S336" t="n">
+        <v>0</v>
+      </c>
+      <c r="T336" t="n">
         <v>1</v>
       </c>
       <c r="U336" t="inlineStr">
@@ -28200,10 +28202,10 @@
       <c r="R337" t="n">
         <v>-3</v>
       </c>
-      <c r="S337" t="b">
-        <v>0</v>
-      </c>
-      <c r="T337" t="b">
+      <c r="S337" t="n">
+        <v>0</v>
+      </c>
+      <c r="T337" t="n">
         <v>1</v>
       </c>
       <c r="U337" t="inlineStr">
@@ -28283,10 +28285,10 @@
       <c r="R338" t="n">
         <v>9</v>
       </c>
-      <c r="S338" t="b">
-        <v>1</v>
-      </c>
-      <c r="T338" t="b">
+      <c r="S338" t="n">
+        <v>1</v>
+      </c>
+      <c r="T338" t="n">
         <v>0</v>
       </c>
       <c r="U338" t="inlineStr">
@@ -28366,10 +28368,10 @@
       <c r="R339" t="n">
         <v>12</v>
       </c>
-      <c r="S339" t="b">
-        <v>1</v>
-      </c>
-      <c r="T339" t="b">
+      <c r="S339" t="n">
+        <v>1</v>
+      </c>
+      <c r="T339" t="n">
         <v>0</v>
       </c>
       <c r="U339" t="inlineStr">
@@ -28449,10 +28451,10 @@
       <c r="R340" t="n">
         <v>-1</v>
       </c>
-      <c r="S340" t="b">
-        <v>0</v>
-      </c>
-      <c r="T340" t="b">
+      <c r="S340" t="n">
+        <v>0</v>
+      </c>
+      <c r="T340" t="n">
         <v>1</v>
       </c>
       <c r="U340" t="inlineStr">
@@ -28532,10 +28534,10 @@
       <c r="R341" t="n">
         <v>7</v>
       </c>
-      <c r="S341" t="b">
-        <v>1</v>
-      </c>
-      <c r="T341" t="b">
+      <c r="S341" t="n">
+        <v>1</v>
+      </c>
+      <c r="T341" t="n">
         <v>0</v>
       </c>
       <c r="U341" t="inlineStr">
@@ -28613,10 +28615,10 @@
       <c r="R342" t="n">
         <v>-4</v>
       </c>
-      <c r="S342" t="b">
-        <v>0</v>
-      </c>
-      <c r="T342" t="b">
+      <c r="S342" t="n">
+        <v>0</v>
+      </c>
+      <c r="T342" t="n">
         <v>1</v>
       </c>
       <c r="U342" t="inlineStr">
@@ -28696,10 +28698,10 @@
       <c r="R343" t="n">
         <v>-2</v>
       </c>
-      <c r="S343" t="b">
-        <v>0</v>
-      </c>
-      <c r="T343" t="b">
+      <c r="S343" t="n">
+        <v>0</v>
+      </c>
+      <c r="T343" t="n">
         <v>1</v>
       </c>
       <c r="U343" t="inlineStr">
@@ -28779,10 +28781,10 @@
       <c r="R344" t="n">
         <v>-9</v>
       </c>
-      <c r="S344" t="b">
-        <v>0</v>
-      </c>
-      <c r="T344" t="b">
+      <c r="S344" t="n">
+        <v>0</v>
+      </c>
+      <c r="T344" t="n">
         <v>1</v>
       </c>
       <c r="U344" t="inlineStr">
@@ -28862,10 +28864,10 @@
       <c r="R345" t="n">
         <v>-9</v>
       </c>
-      <c r="S345" t="b">
-        <v>0</v>
-      </c>
-      <c r="T345" t="b">
+      <c r="S345" t="n">
+        <v>0</v>
+      </c>
+      <c r="T345" t="n">
         <v>1</v>
       </c>
       <c r="U345" t="inlineStr">
@@ -28945,10 +28947,10 @@
       <c r="R346" t="n">
         <v>2</v>
       </c>
-      <c r="S346" t="b">
-        <v>1</v>
-      </c>
-      <c r="T346" t="b">
+      <c r="S346" t="n">
+        <v>1</v>
+      </c>
+      <c r="T346" t="n">
         <v>0</v>
       </c>
       <c r="U346" t="inlineStr">
@@ -29026,10 +29028,10 @@
       <c r="R347" t="n">
         <v>-5</v>
       </c>
-      <c r="S347" t="b">
-        <v>0</v>
-      </c>
-      <c r="T347" t="b">
+      <c r="S347" t="n">
+        <v>0</v>
+      </c>
+      <c r="T347" t="n">
         <v>1</v>
       </c>
       <c r="U347" t="inlineStr">
@@ -29107,10 +29109,10 @@
       <c r="R348" t="n">
         <v>-6</v>
       </c>
-      <c r="S348" t="b">
-        <v>0</v>
-      </c>
-      <c r="T348" t="b">
+      <c r="S348" t="n">
+        <v>0</v>
+      </c>
+      <c r="T348" t="n">
         <v>1</v>
       </c>
       <c r="U348" t="inlineStr">
@@ -29190,10 +29192,10 @@
       <c r="R349" t="n">
         <v>6</v>
       </c>
-      <c r="S349" t="b">
-        <v>1</v>
-      </c>
-      <c r="T349" t="b">
+      <c r="S349" t="n">
+        <v>1</v>
+      </c>
+      <c r="T349" t="n">
         <v>0</v>
       </c>
       <c r="U349" t="inlineStr">
@@ -29273,10 +29275,10 @@
       <c r="R350" t="n">
         <v>5</v>
       </c>
-      <c r="S350" t="b">
-        <v>1</v>
-      </c>
-      <c r="T350" t="b">
+      <c r="S350" t="n">
+        <v>1</v>
+      </c>
+      <c r="T350" t="n">
         <v>0</v>
       </c>
       <c r="U350" t="inlineStr">
@@ -29502,10 +29504,10 @@
       <c r="R353" t="n">
         <v>7</v>
       </c>
-      <c r="S353" t="b">
-        <v>1</v>
-      </c>
-      <c r="T353" t="b">
+      <c r="S353" t="n">
+        <v>1</v>
+      </c>
+      <c r="T353" t="n">
         <v>0</v>
       </c>
       <c r="U353" t="inlineStr">
@@ -29585,10 +29587,10 @@
       <c r="R354" t="n">
         <v>-5</v>
       </c>
-      <c r="S354" t="b">
-        <v>0</v>
-      </c>
-      <c r="T354" t="b">
+      <c r="S354" t="n">
+        <v>0</v>
+      </c>
+      <c r="T354" t="n">
         <v>1</v>
       </c>
       <c r="U354" t="inlineStr">
@@ -29668,10 +29670,10 @@
       <c r="R355" t="n">
         <v>9</v>
       </c>
-      <c r="S355" t="b">
-        <v>1</v>
-      </c>
-      <c r="T355" t="b">
+      <c r="S355" t="n">
+        <v>1</v>
+      </c>
+      <c r="T355" t="n">
         <v>0</v>
       </c>
       <c r="U355" t="inlineStr">
@@ -29751,10 +29753,10 @@
       <c r="R356" t="n">
         <v>-6</v>
       </c>
-      <c r="S356" t="b">
-        <v>0</v>
-      </c>
-      <c r="T356" t="b">
+      <c r="S356" t="n">
+        <v>0</v>
+      </c>
+      <c r="T356" t="n">
         <v>1</v>
       </c>
       <c r="U356" t="inlineStr">
@@ -29834,10 +29836,10 @@
       <c r="R357" t="n">
         <v>9</v>
       </c>
-      <c r="S357" t="b">
-        <v>1</v>
-      </c>
-      <c r="T357" t="b">
+      <c r="S357" t="n">
+        <v>1</v>
+      </c>
+      <c r="T357" t="n">
         <v>0</v>
       </c>
       <c r="U357" t="inlineStr">
@@ -29917,10 +29919,10 @@
       <c r="R358" t="n">
         <v>2</v>
       </c>
-      <c r="S358" t="b">
-        <v>1</v>
-      </c>
-      <c r="T358" t="b">
+      <c r="S358" t="n">
+        <v>1</v>
+      </c>
+      <c r="T358" t="n">
         <v>0</v>
       </c>
       <c r="U358" t="inlineStr">
@@ -30000,10 +30002,10 @@
       <c r="R359" t="n">
         <v>-11</v>
       </c>
-      <c r="S359" t="b">
-        <v>0</v>
-      </c>
-      <c r="T359" t="b">
+      <c r="S359" t="n">
+        <v>0</v>
+      </c>
+      <c r="T359" t="n">
         <v>1</v>
       </c>
       <c r="U359" t="inlineStr">
@@ -30083,10 +30085,10 @@
       <c r="R360" t="n">
         <v>-6</v>
       </c>
-      <c r="S360" t="b">
-        <v>0</v>
-      </c>
-      <c r="T360" t="b">
+      <c r="S360" t="n">
+        <v>0</v>
+      </c>
+      <c r="T360" t="n">
         <v>1</v>
       </c>
       <c r="U360" t="inlineStr">
@@ -30166,10 +30168,10 @@
       <c r="R361" t="n">
         <v>-10</v>
       </c>
-      <c r="S361" t="b">
-        <v>0</v>
-      </c>
-      <c r="T361" t="b">
+      <c r="S361" t="n">
+        <v>0</v>
+      </c>
+      <c r="T361" t="n">
         <v>1</v>
       </c>
       <c r="U361" t="inlineStr">
@@ -30249,10 +30251,10 @@
       <c r="R362" t="n">
         <v>14</v>
       </c>
-      <c r="S362" t="b">
-        <v>1</v>
-      </c>
-      <c r="T362" t="b">
+      <c r="S362" t="n">
+        <v>1</v>
+      </c>
+      <c r="T362" t="n">
         <v>0</v>
       </c>
       <c r="U362" t="inlineStr">
@@ -30332,10 +30334,10 @@
       <c r="R363" t="n">
         <v>-2</v>
       </c>
-      <c r="S363" t="b">
-        <v>0</v>
-      </c>
-      <c r="T363" t="b">
+      <c r="S363" t="n">
+        <v>0</v>
+      </c>
+      <c r="T363" t="n">
         <v>1</v>
       </c>
       <c r="U363" t="inlineStr">
@@ -30415,10 +30417,10 @@
       <c r="R364" t="n">
         <v>8</v>
       </c>
-      <c r="S364" t="b">
-        <v>1</v>
-      </c>
-      <c r="T364" t="b">
+      <c r="S364" t="n">
+        <v>1</v>
+      </c>
+      <c r="T364" t="n">
         <v>0</v>
       </c>
       <c r="U364" t="inlineStr">
@@ -30498,10 +30500,10 @@
       <c r="R365" t="n">
         <v>-5</v>
       </c>
-      <c r="S365" t="b">
-        <v>0</v>
-      </c>
-      <c r="T365" t="b">
+      <c r="S365" t="n">
+        <v>0</v>
+      </c>
+      <c r="T365" t="n">
         <v>1</v>
       </c>
       <c r="U365" t="inlineStr">
@@ -30581,10 +30583,10 @@
       <c r="R366" t="n">
         <v>-5</v>
       </c>
-      <c r="S366" t="b">
-        <v>0</v>
-      </c>
-      <c r="T366" t="b">
+      <c r="S366" t="n">
+        <v>0</v>
+      </c>
+      <c r="T366" t="n">
         <v>1</v>
       </c>
       <c r="U366" t="inlineStr">
@@ -30664,10 +30666,10 @@
       <c r="R367" t="n">
         <v>4</v>
       </c>
-      <c r="S367" t="b">
-        <v>1</v>
-      </c>
-      <c r="T367" t="b">
+      <c r="S367" t="n">
+        <v>1</v>
+      </c>
+      <c r="T367" t="n">
         <v>0</v>
       </c>
       <c r="U367" t="inlineStr">
@@ -30747,10 +30749,10 @@
       <c r="R368" t="n">
         <v>-1</v>
       </c>
-      <c r="S368" t="b">
-        <v>0</v>
-      </c>
-      <c r="T368" t="b">
+      <c r="S368" t="n">
+        <v>0</v>
+      </c>
+      <c r="T368" t="n">
         <v>1</v>
       </c>
       <c r="U368" t="inlineStr">
@@ -30830,10 +30832,10 @@
       <c r="R369" t="n">
         <v>0</v>
       </c>
-      <c r="S369" t="b">
-        <v>0</v>
-      </c>
-      <c r="T369" t="b">
+      <c r="S369" t="n">
+        <v>0</v>
+      </c>
+      <c r="T369" t="n">
         <v>0</v>
       </c>
       <c r="U369" t="inlineStr">
@@ -30913,10 +30915,10 @@
       <c r="R370" t="n">
         <v>7</v>
       </c>
-      <c r="S370" t="b">
-        <v>1</v>
-      </c>
-      <c r="T370" t="b">
+      <c r="S370" t="n">
+        <v>1</v>
+      </c>
+      <c r="T370" t="n">
         <v>0</v>
       </c>
       <c r="U370" t="inlineStr">
@@ -30996,10 +30998,10 @@
       <c r="R371" t="n">
         <v>-2</v>
       </c>
-      <c r="S371" t="b">
-        <v>0</v>
-      </c>
-      <c r="T371" t="b">
+      <c r="S371" t="n">
+        <v>0</v>
+      </c>
+      <c r="T371" t="n">
         <v>1</v>
       </c>
       <c r="U371" t="inlineStr">
@@ -31079,10 +31081,10 @@
       <c r="R372" t="n">
         <v>-5</v>
       </c>
-      <c r="S372" t="b">
-        <v>0</v>
-      </c>
-      <c r="T372" t="b">
+      <c r="S372" t="n">
+        <v>0</v>
+      </c>
+      <c r="T372" t="n">
         <v>1</v>
       </c>
       <c r="U372" t="inlineStr">
@@ -31235,10 +31237,10 @@
       <c r="R374" t="n">
         <v>-1</v>
       </c>
-      <c r="S374" t="b">
-        <v>0</v>
-      </c>
-      <c r="T374" t="b">
+      <c r="S374" t="n">
+        <v>0</v>
+      </c>
+      <c r="T374" t="n">
         <v>1</v>
       </c>
       <c r="U374" t="inlineStr">
@@ -31391,10 +31393,10 @@
       <c r="R376" t="n">
         <v>6</v>
       </c>
-      <c r="S376" t="b">
-        <v>1</v>
-      </c>
-      <c r="T376" t="b">
+      <c r="S376" t="n">
+        <v>1</v>
+      </c>
+      <c r="T376" t="n">
         <v>0</v>
       </c>
       <c r="U376" t="inlineStr">
@@ -31474,10 +31476,10 @@
       <c r="R377" t="n">
         <v>2</v>
       </c>
-      <c r="S377" t="b">
-        <v>1</v>
-      </c>
-      <c r="T377" t="b">
+      <c r="S377" t="n">
+        <v>1</v>
+      </c>
+      <c r="T377" t="n">
         <v>0</v>
       </c>
       <c r="U377" t="inlineStr">
@@ -31557,10 +31559,10 @@
       <c r="R378" t="n">
         <v>8</v>
       </c>
-      <c r="S378" t="b">
-        <v>1</v>
-      </c>
-      <c r="T378" t="b">
+      <c r="S378" t="n">
+        <v>1</v>
+      </c>
+      <c r="T378" t="n">
         <v>0</v>
       </c>
       <c r="U378" t="inlineStr">
@@ -31640,10 +31642,10 @@
       <c r="R379" t="n">
         <v>11</v>
       </c>
-      <c r="S379" t="b">
-        <v>1</v>
-      </c>
-      <c r="T379" t="b">
+      <c r="S379" t="n">
+        <v>1</v>
+      </c>
+      <c r="T379" t="n">
         <v>0</v>
       </c>
       <c r="U379" t="inlineStr">
@@ -31723,10 +31725,10 @@
       <c r="R380" t="n">
         <v>-3</v>
       </c>
-      <c r="S380" t="b">
-        <v>0</v>
-      </c>
-      <c r="T380" t="b">
+      <c r="S380" t="n">
+        <v>0</v>
+      </c>
+      <c r="T380" t="n">
         <v>1</v>
       </c>
       <c r="U380" t="inlineStr">
@@ -31806,10 +31808,10 @@
       <c r="R381" t="n">
         <v>-6</v>
       </c>
-      <c r="S381" t="b">
-        <v>0</v>
-      </c>
-      <c r="T381" t="b">
+      <c r="S381" t="n">
+        <v>0</v>
+      </c>
+      <c r="T381" t="n">
         <v>1</v>
       </c>
       <c r="U381" t="inlineStr">
@@ -31889,10 +31891,10 @@
       <c r="R382" t="n">
         <v>10</v>
       </c>
-      <c r="S382" t="b">
-        <v>1</v>
-      </c>
-      <c r="T382" t="b">
+      <c r="S382" t="n">
+        <v>1</v>
+      </c>
+      <c r="T382" t="n">
         <v>0</v>
       </c>
       <c r="U382" t="inlineStr">
@@ -31972,10 +31974,10 @@
       <c r="R383" t="n">
         <v>16</v>
       </c>
-      <c r="S383" t="b">
-        <v>1</v>
-      </c>
-      <c r="T383" t="b">
+      <c r="S383" t="n">
+        <v>1</v>
+      </c>
+      <c r="T383" t="n">
         <v>0</v>
       </c>
       <c r="U383" t="inlineStr">
@@ -32055,10 +32057,10 @@
       <c r="R384" t="n">
         <v>-5</v>
       </c>
-      <c r="S384" t="b">
-        <v>0</v>
-      </c>
-      <c r="T384" t="b">
+      <c r="S384" t="n">
+        <v>0</v>
+      </c>
+      <c r="T384" t="n">
         <v>1</v>
       </c>
       <c r="U384" t="inlineStr">
@@ -32138,10 +32140,10 @@
       <c r="R385" t="n">
         <v>-5</v>
       </c>
-      <c r="S385" t="b">
-        <v>0</v>
-      </c>
-      <c r="T385" t="b">
+      <c r="S385" t="n">
+        <v>0</v>
+      </c>
+      <c r="T385" t="n">
         <v>1</v>
       </c>
       <c r="U385" t="inlineStr">
@@ -32221,10 +32223,10 @@
       <c r="R386" t="n">
         <v>9</v>
       </c>
-      <c r="S386" t="b">
-        <v>1</v>
-      </c>
-      <c r="T386" t="b">
+      <c r="S386" t="n">
+        <v>1</v>
+      </c>
+      <c r="T386" t="n">
         <v>0</v>
       </c>
       <c r="U386" t="inlineStr">
@@ -32304,10 +32306,10 @@
       <c r="R387" t="n">
         <v>12</v>
       </c>
-      <c r="S387" t="b">
-        <v>1</v>
-      </c>
-      <c r="T387" t="b">
+      <c r="S387" t="n">
+        <v>1</v>
+      </c>
+      <c r="T387" t="n">
         <v>0</v>
       </c>
       <c r="U387" t="inlineStr">
@@ -32387,10 +32389,10 @@
       <c r="R388" t="n">
         <v>5</v>
       </c>
-      <c r="S388" t="b">
-        <v>1</v>
-      </c>
-      <c r="T388" t="b">
+      <c r="S388" t="n">
+        <v>1</v>
+      </c>
+      <c r="T388" t="n">
         <v>0</v>
       </c>
       <c r="U388" t="inlineStr">
@@ -32470,10 +32472,10 @@
       <c r="R389" t="n">
         <v>17</v>
       </c>
-      <c r="S389" t="b">
-        <v>1</v>
-      </c>
-      <c r="T389" t="b">
+      <c r="S389" t="n">
+        <v>1</v>
+      </c>
+      <c r="T389" t="n">
         <v>0</v>
       </c>
       <c r="U389" t="inlineStr">
@@ -32553,10 +32555,10 @@
       <c r="R390" t="n">
         <v>14</v>
       </c>
-      <c r="S390" t="b">
-        <v>1</v>
-      </c>
-      <c r="T390" t="b">
+      <c r="S390" t="n">
+        <v>1</v>
+      </c>
+      <c r="T390" t="n">
         <v>0</v>
       </c>
       <c r="U390" t="inlineStr">
@@ -32636,10 +32638,10 @@
       <c r="R391" t="n">
         <v>10</v>
       </c>
-      <c r="S391" t="b">
-        <v>1</v>
-      </c>
-      <c r="T391" t="b">
+      <c r="S391" t="n">
+        <v>1</v>
+      </c>
+      <c r="T391" t="n">
         <v>0</v>
       </c>
       <c r="U391" t="inlineStr">
@@ -32719,10 +32721,10 @@
       <c r="R392" t="n">
         <v>16</v>
       </c>
-      <c r="S392" t="b">
-        <v>1</v>
-      </c>
-      <c r="T392" t="b">
+      <c r="S392" t="n">
+        <v>1</v>
+      </c>
+      <c r="T392" t="n">
         <v>0</v>
       </c>
       <c r="U392" t="inlineStr">
@@ -32802,10 +32804,10 @@
       <c r="R393" t="n">
         <v>0</v>
       </c>
-      <c r="S393" t="b">
-        <v>0</v>
-      </c>
-      <c r="T393" t="b">
+      <c r="S393" t="n">
+        <v>0</v>
+      </c>
+      <c r="T393" t="n">
         <v>0</v>
       </c>
       <c r="U393" t="inlineStr">
@@ -32885,10 +32887,10 @@
       <c r="R394" t="n">
         <v>9</v>
       </c>
-      <c r="S394" t="b">
-        <v>1</v>
-      </c>
-      <c r="T394" t="b">
+      <c r="S394" t="n">
+        <v>1</v>
+      </c>
+      <c r="T394" t="n">
         <v>0</v>
       </c>
       <c r="U394" t="inlineStr">
@@ -32968,10 +32970,10 @@
       <c r="R395" t="n">
         <v>4</v>
       </c>
-      <c r="S395" t="b">
-        <v>1</v>
-      </c>
-      <c r="T395" t="b">
+      <c r="S395" t="n">
+        <v>1</v>
+      </c>
+      <c r="T395" t="n">
         <v>0</v>
       </c>
       <c r="U395" t="inlineStr">
@@ -33051,10 +33053,10 @@
       <c r="R396" t="n">
         <v>11</v>
       </c>
-      <c r="S396" t="b">
-        <v>1</v>
-      </c>
-      <c r="T396" t="b">
+      <c r="S396" t="n">
+        <v>1</v>
+      </c>
+      <c r="T396" t="n">
         <v>0</v>
       </c>
       <c r="U396" t="inlineStr">
@@ -33134,10 +33136,10 @@
       <c r="R397" t="n">
         <v>-7</v>
       </c>
-      <c r="S397" t="b">
-        <v>0</v>
-      </c>
-      <c r="T397" t="b">
+      <c r="S397" t="n">
+        <v>0</v>
+      </c>
+      <c r="T397" t="n">
         <v>1</v>
       </c>
       <c r="U397" t="inlineStr">
@@ -33290,10 +33292,10 @@
       <c r="R399" t="n">
         <v>37</v>
       </c>
-      <c r="S399" t="b">
-        <v>1</v>
-      </c>
-      <c r="T399" t="b">
+      <c r="S399" t="n">
+        <v>1</v>
+      </c>
+      <c r="T399" t="n">
         <v>0</v>
       </c>
       <c r="U399" t="inlineStr">
@@ -33373,10 +33375,10 @@
       <c r="R400" t="n">
         <v>-2</v>
       </c>
-      <c r="S400" t="b">
-        <v>0</v>
-      </c>
-      <c r="T400" t="b">
+      <c r="S400" t="n">
+        <v>0</v>
+      </c>
+      <c r="T400" t="n">
         <v>1</v>
       </c>
       <c r="U400" t="inlineStr">
@@ -33456,10 +33458,10 @@
       <c r="R401" t="n">
         <v>4</v>
       </c>
-      <c r="S401" t="b">
-        <v>1</v>
-      </c>
-      <c r="T401" t="b">
+      <c r="S401" t="n">
+        <v>1</v>
+      </c>
+      <c r="T401" t="n">
         <v>0</v>
       </c>
       <c r="U401" t="inlineStr">
@@ -33539,10 +33541,10 @@
       <c r="R402" t="n">
         <v>-4</v>
       </c>
-      <c r="S402" t="b">
-        <v>0</v>
-      </c>
-      <c r="T402" t="b">
+      <c r="S402" t="n">
+        <v>0</v>
+      </c>
+      <c r="T402" t="n">
         <v>1</v>
       </c>
       <c r="U402" t="inlineStr">
@@ -33622,10 +33624,10 @@
       <c r="R403" t="n">
         <v>-11</v>
       </c>
-      <c r="S403" t="b">
-        <v>0</v>
-      </c>
-      <c r="T403" t="b">
+      <c r="S403" t="n">
+        <v>0</v>
+      </c>
+      <c r="T403" t="n">
         <v>1</v>
       </c>
       <c r="U403" t="inlineStr">
@@ -33705,10 +33707,10 @@
       <c r="R404" t="n">
         <v>-4</v>
       </c>
-      <c r="S404" t="b">
-        <v>0</v>
-      </c>
-      <c r="T404" t="b">
+      <c r="S404" t="n">
+        <v>0</v>
+      </c>
+      <c r="T404" t="n">
         <v>1</v>
       </c>
       <c r="U404" t="inlineStr">
@@ -33788,10 +33790,10 @@
       <c r="R405" t="n">
         <v>36</v>
       </c>
-      <c r="S405" t="b">
-        <v>1</v>
-      </c>
-      <c r="T405" t="b">
+      <c r="S405" t="n">
+        <v>1</v>
+      </c>
+      <c r="T405" t="n">
         <v>0</v>
       </c>
       <c r="U405" t="inlineStr">
@@ -33871,10 +33873,10 @@
       <c r="R406" t="n">
         <v>-5</v>
       </c>
-      <c r="S406" t="b">
-        <v>0</v>
-      </c>
-      <c r="T406" t="b">
+      <c r="S406" t="n">
+        <v>0</v>
+      </c>
+      <c r="T406" t="n">
         <v>1</v>
       </c>
       <c r="U406" t="inlineStr">
@@ -33954,10 +33956,10 @@
       <c r="R407" t="n">
         <v>7</v>
       </c>
-      <c r="S407" t="b">
-        <v>1</v>
-      </c>
-      <c r="T407" t="b">
+      <c r="S407" t="n">
+        <v>1</v>
+      </c>
+      <c r="T407" t="n">
         <v>0</v>
       </c>
       <c r="U407" t="inlineStr">
@@ -34037,10 +34039,10 @@
       <c r="R408" t="n">
         <v>1</v>
       </c>
-      <c r="S408" t="b">
-        <v>1</v>
-      </c>
-      <c r="T408" t="b">
+      <c r="S408" t="n">
+        <v>1</v>
+      </c>
+      <c r="T408" t="n">
         <v>0</v>
       </c>
       <c r="U408" t="inlineStr">
@@ -34120,10 +34122,10 @@
       <c r="R409" t="n">
         <v>5</v>
       </c>
-      <c r="S409" t="b">
-        <v>1</v>
-      </c>
-      <c r="T409" t="b">
+      <c r="S409" t="n">
+        <v>1</v>
+      </c>
+      <c r="T409" t="n">
         <v>0</v>
       </c>
       <c r="U409" t="inlineStr">
@@ -34203,10 +34205,10 @@
       <c r="R410" t="n">
         <v>-1</v>
       </c>
-      <c r="S410" t="b">
-        <v>0</v>
-      </c>
-      <c r="T410" t="b">
+      <c r="S410" t="n">
+        <v>0</v>
+      </c>
+      <c r="T410" t="n">
         <v>1</v>
       </c>
       <c r="U410" t="inlineStr">
@@ -34286,10 +34288,10 @@
       <c r="R411" t="n">
         <v>-6</v>
       </c>
-      <c r="S411" t="b">
-        <v>0</v>
-      </c>
-      <c r="T411" t="b">
+      <c r="S411" t="n">
+        <v>0</v>
+      </c>
+      <c r="T411" t="n">
         <v>1</v>
       </c>
       <c r="U411" t="inlineStr">
@@ -34369,10 +34371,10 @@
       <c r="R412" t="n">
         <v>-5</v>
       </c>
-      <c r="S412" t="b">
-        <v>0</v>
-      </c>
-      <c r="T412" t="b">
+      <c r="S412" t="n">
+        <v>0</v>
+      </c>
+      <c r="T412" t="n">
         <v>1</v>
       </c>
       <c r="U412" t="inlineStr">
@@ -34452,10 +34454,10 @@
       <c r="R413" t="n">
         <v>-1</v>
       </c>
-      <c r="S413" t="b">
-        <v>0</v>
-      </c>
-      <c r="T413" t="b">
+      <c r="S413" t="n">
+        <v>0</v>
+      </c>
+      <c r="T413" t="n">
         <v>1</v>
       </c>
       <c r="U413" t="inlineStr">
@@ -34531,10 +34533,10 @@
       <c r="R414" t="n">
         <v>11</v>
       </c>
-      <c r="S414" t="b">
-        <v>1</v>
-      </c>
-      <c r="T414" t="b">
+      <c r="S414" t="n">
+        <v>1</v>
+      </c>
+      <c r="T414" t="n">
         <v>0</v>
       </c>
       <c r="U414" t="inlineStr">
@@ -34614,10 +34616,10 @@
       <c r="R415" t="n">
         <v>5</v>
       </c>
-      <c r="S415" t="b">
-        <v>1</v>
-      </c>
-      <c r="T415" t="b">
+      <c r="S415" t="n">
+        <v>1</v>
+      </c>
+      <c r="T415" t="n">
         <v>0</v>
       </c>
       <c r="U415" t="inlineStr">
@@ -34697,10 +34699,10 @@
       <c r="R416" t="n">
         <v>-5</v>
       </c>
-      <c r="S416" t="b">
-        <v>0</v>
-      </c>
-      <c r="T416" t="b">
+      <c r="S416" t="n">
+        <v>0</v>
+      </c>
+      <c r="T416" t="n">
         <v>1</v>
       </c>
       <c r="U416" t="inlineStr">
@@ -34780,10 +34782,10 @@
       <c r="R417" t="n">
         <v>0</v>
       </c>
-      <c r="S417" t="b">
-        <v>0</v>
-      </c>
-      <c r="T417" t="b">
+      <c r="S417" t="n">
+        <v>0</v>
+      </c>
+      <c r="T417" t="n">
         <v>0</v>
       </c>
       <c r="U417" t="inlineStr">
@@ -34863,10 +34865,10 @@
       <c r="R418" t="n">
         <v>35</v>
       </c>
-      <c r="S418" t="b">
-        <v>1</v>
-      </c>
-      <c r="T418" t="b">
+      <c r="S418" t="n">
+        <v>1</v>
+      </c>
+      <c r="T418" t="n">
         <v>0</v>
       </c>
       <c r="U418" t="inlineStr">
@@ -35017,10 +35019,10 @@
       <c r="R420" t="n">
         <v>17</v>
       </c>
-      <c r="S420" t="b">
-        <v>1</v>
-      </c>
-      <c r="T420" t="b">
+      <c r="S420" t="n">
+        <v>1</v>
+      </c>
+      <c r="T420" t="n">
         <v>0</v>
       </c>
       <c r="U420" t="inlineStr">
@@ -35100,10 +35102,10 @@
       <c r="R421" t="n">
         <v>2</v>
       </c>
-      <c r="S421" t="b">
-        <v>1</v>
-      </c>
-      <c r="T421" t="b">
+      <c r="S421" t="n">
+        <v>1</v>
+      </c>
+      <c r="T421" t="n">
         <v>0</v>
       </c>
       <c r="U421" t="inlineStr">
@@ -35183,10 +35185,10 @@
       <c r="R422" t="n">
         <v>-4</v>
       </c>
-      <c r="S422" t="b">
-        <v>0</v>
-      </c>
-      <c r="T422" t="b">
+      <c r="S422" t="n">
+        <v>0</v>
+      </c>
+      <c r="T422" t="n">
         <v>1</v>
       </c>
       <c r="U422" t="inlineStr">
@@ -35266,10 +35268,10 @@
       <c r="R423" t="n">
         <v>-13</v>
       </c>
-      <c r="S423" t="b">
-        <v>0</v>
-      </c>
-      <c r="T423" t="b">
+      <c r="S423" t="n">
+        <v>0</v>
+      </c>
+      <c r="T423" t="n">
         <v>1</v>
       </c>
       <c r="U423" t="inlineStr">
@@ -35349,10 +35351,10 @@
       <c r="R424" t="n">
         <v>9</v>
       </c>
-      <c r="S424" t="b">
-        <v>1</v>
-      </c>
-      <c r="T424" t="b">
+      <c r="S424" t="n">
+        <v>1</v>
+      </c>
+      <c r="T424" t="n">
         <v>0</v>
       </c>
       <c r="U424" t="inlineStr">
@@ -35432,10 +35434,10 @@
       <c r="R425" t="n">
         <v>9</v>
       </c>
-      <c r="S425" t="b">
-        <v>1</v>
-      </c>
-      <c r="T425" t="b">
+      <c r="S425" t="n">
+        <v>1</v>
+      </c>
+      <c r="T425" t="n">
         <v>0</v>
       </c>
       <c r="U425" t="inlineStr">
@@ -35515,10 +35517,10 @@
       <c r="R426" t="n">
         <v>9</v>
       </c>
-      <c r="S426" t="b">
-        <v>1</v>
-      </c>
-      <c r="T426" t="b">
+      <c r="S426" t="n">
+        <v>1</v>
+      </c>
+      <c r="T426" t="n">
         <v>0</v>
       </c>
       <c r="U426" t="inlineStr">
@@ -35596,10 +35598,10 @@
       <c r="R427" t="n">
         <v>5</v>
       </c>
-      <c r="S427" t="b">
-        <v>1</v>
-      </c>
-      <c r="T427" t="b">
+      <c r="S427" t="n">
+        <v>1</v>
+      </c>
+      <c r="T427" t="n">
         <v>0</v>
       </c>
       <c r="U427" t="inlineStr">
@@ -35679,10 +35681,10 @@
       <c r="R428" t="n">
         <v>5</v>
       </c>
-      <c r="S428" t="b">
-        <v>1</v>
-      </c>
-      <c r="T428" t="b">
+      <c r="S428" t="n">
+        <v>1</v>
+      </c>
+      <c r="T428" t="n">
         <v>0</v>
       </c>
       <c r="U428" t="inlineStr">
@@ -35762,10 +35764,10 @@
       <c r="R429" t="n">
         <v>36</v>
       </c>
-      <c r="S429" t="b">
-        <v>1</v>
-      </c>
-      <c r="T429" t="b">
+      <c r="S429" t="n">
+        <v>1</v>
+      </c>
+      <c r="T429" t="n">
         <v>0</v>
       </c>
       <c r="U429" t="inlineStr">
